--- a/Capstone/Fase 1/Evidencias Grupales/Carta Gantt.xlsx
+++ b/Capstone/Fase 1/Evidencias Grupales/Carta Gantt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB45FB6-84BD-48FA-A2B2-A812CF6F465F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C131F980-867F-4B0B-9A2B-927851B8F382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1058,7 +1058,7 @@
     <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1108,9 +1108,6 @@
     <xf numFmtId="9" fontId="4" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1240,9 +1237,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="17" xfId="11" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="7" fillId="7" borderId="17" xfId="10" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1303,6 +1297,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1335,18 +1341,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -1963,14 +1957,14 @@
   <dimension ref="A1:DQ36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="23" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" style="22" customWidth="1"/>
     <col min="2" max="2" width="29.42578125" customWidth="1"/>
     <col min="3" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" style="5" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" customWidth="1"/>
     <col min="7" max="7" width="2" customWidth="1"/>
-    <col min="8" max="8" width="1.85546875" style="47" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="1.85546875" style="46" hidden="1" customWidth="1"/>
     <col min="9" max="15" width="4.7109375" customWidth="1"/>
     <col min="16" max="16" width="5" style="3" customWidth="1"/>
     <col min="17" max="18" width="5.140625" style="3" customWidth="1"/>
@@ -2020,550 +2014,550 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:121" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="46"/>
+      <c r="F1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="45"/>
     </row>
     <row r="2" spans="1:121" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="93" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="94"/>
-      <c r="E2" s="97">
+      <c r="D2" s="96"/>
+      <c r="E2" s="99">
         <f>DATE(2025,8,12)</f>
         <v>45881</v>
       </c>
-      <c r="F2" s="97"/>
+      <c r="F2" s="99"/>
     </row>
-    <row r="3" spans="1:121" s="26" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+    <row r="3" spans="1:121" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="C3" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="96"/>
-      <c r="E3" s="61">
+      <c r="D3" s="98"/>
+      <c r="E3" s="60">
         <v>1</v>
       </c>
-      <c r="H3" s="62"/>
-      <c r="I3" s="99">
+      <c r="H3" s="61"/>
+      <c r="I3" s="86">
         <f>I4</f>
         <v>45880</v>
       </c>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99">
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="86">
         <f>N4</f>
         <v>45887</v>
       </c>
-      <c r="O3" s="99"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99">
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="86"/>
+      <c r="S3" s="86">
         <f>S4</f>
         <v>45894</v>
       </c>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="99"/>
-      <c r="X3" s="99">
+      <c r="T3" s="86"/>
+      <c r="U3" s="86"/>
+      <c r="V3" s="86"/>
+      <c r="W3" s="86"/>
+      <c r="X3" s="86">
         <f>X4</f>
         <v>45901</v>
       </c>
-      <c r="Y3" s="99"/>
-      <c r="Z3" s="99"/>
-      <c r="AA3" s="99"/>
-      <c r="AB3" s="99"/>
-      <c r="AC3" s="99">
+      <c r="Y3" s="86"/>
+      <c r="Z3" s="86"/>
+      <c r="AA3" s="86"/>
+      <c r="AB3" s="86"/>
+      <c r="AC3" s="86">
         <f t="shared" ref="AC3" si="0">AC4</f>
         <v>45908</v>
       </c>
-      <c r="AD3" s="99"/>
-      <c r="AE3" s="99"/>
-      <c r="AF3" s="99"/>
-      <c r="AG3" s="99"/>
-      <c r="AH3" s="99">
+      <c r="AD3" s="86"/>
+      <c r="AE3" s="86"/>
+      <c r="AF3" s="86"/>
+      <c r="AG3" s="86"/>
+      <c r="AH3" s="86">
         <f t="shared" ref="AH3" si="1">AH4</f>
         <v>45915</v>
       </c>
-      <c r="AI3" s="99"/>
-      <c r="AJ3" s="99"/>
-      <c r="AK3" s="99"/>
-      <c r="AL3" s="99"/>
-      <c r="AM3" s="99">
+      <c r="AI3" s="86"/>
+      <c r="AJ3" s="86"/>
+      <c r="AK3" s="86"/>
+      <c r="AL3" s="86"/>
+      <c r="AM3" s="86">
         <f t="shared" ref="AM3" si="2">AM4</f>
         <v>45922</v>
       </c>
-      <c r="AN3" s="99"/>
-      <c r="AO3" s="99"/>
-      <c r="AP3" s="99"/>
-      <c r="AQ3" s="99"/>
-      <c r="AR3" s="99">
+      <c r="AN3" s="86"/>
+      <c r="AO3" s="86"/>
+      <c r="AP3" s="86"/>
+      <c r="AQ3" s="86"/>
+      <c r="AR3" s="86">
         <f>AR4</f>
         <v>45929</v>
       </c>
-      <c r="AS3" s="99"/>
-      <c r="AT3" s="99"/>
-      <c r="AU3" s="99"/>
-      <c r="AV3" s="99"/>
-      <c r="AW3" s="99">
+      <c r="AS3" s="86"/>
+      <c r="AT3" s="86"/>
+      <c r="AU3" s="86"/>
+      <c r="AV3" s="86"/>
+      <c r="AW3" s="86">
         <f t="shared" ref="AW3" si="3">AW4</f>
         <v>45936</v>
       </c>
-      <c r="AX3" s="99"/>
-      <c r="AY3" s="99"/>
-      <c r="AZ3" s="99"/>
-      <c r="BA3" s="99"/>
-      <c r="BB3" s="99">
+      <c r="AX3" s="86"/>
+      <c r="AY3" s="86"/>
+      <c r="AZ3" s="86"/>
+      <c r="BA3" s="86"/>
+      <c r="BB3" s="86">
         <f t="shared" ref="BB3" si="4">BB4</f>
         <v>45943</v>
       </c>
-      <c r="BC3" s="99"/>
-      <c r="BD3" s="99"/>
-      <c r="BE3" s="99"/>
-      <c r="BF3" s="99"/>
-      <c r="BG3" s="99">
+      <c r="BC3" s="86"/>
+      <c r="BD3" s="86"/>
+      <c r="BE3" s="86"/>
+      <c r="BF3" s="86"/>
+      <c r="BG3" s="86">
         <f t="shared" ref="BG3" si="5">BG4</f>
         <v>45950</v>
       </c>
-      <c r="BH3" s="99"/>
-      <c r="BI3" s="99"/>
-      <c r="BJ3" s="99"/>
-      <c r="BK3" s="99"/>
-      <c r="BL3" s="99">
+      <c r="BH3" s="86"/>
+      <c r="BI3" s="86"/>
+      <c r="BJ3" s="86"/>
+      <c r="BK3" s="86"/>
+      <c r="BL3" s="86">
         <f t="shared" ref="BL3" si="6">BL4</f>
         <v>45957</v>
       </c>
-      <c r="BM3" s="99"/>
-      <c r="BN3" s="99"/>
-      <c r="BO3" s="99"/>
-      <c r="BP3" s="99"/>
-      <c r="BQ3" s="99">
+      <c r="BM3" s="86"/>
+      <c r="BN3" s="86"/>
+      <c r="BO3" s="86"/>
+      <c r="BP3" s="86"/>
+      <c r="BQ3" s="86">
         <f t="shared" ref="BQ3" si="7">BQ4</f>
         <v>45964</v>
       </c>
-      <c r="BR3" s="99"/>
-      <c r="BS3" s="99"/>
-      <c r="BT3" s="99"/>
-      <c r="BU3" s="99"/>
-      <c r="BV3" s="99">
+      <c r="BR3" s="86"/>
+      <c r="BS3" s="86"/>
+      <c r="BT3" s="86"/>
+      <c r="BU3" s="86"/>
+      <c r="BV3" s="86">
         <f t="shared" ref="BV3" si="8">BV4</f>
         <v>45971</v>
       </c>
-      <c r="BW3" s="99"/>
-      <c r="BX3" s="99"/>
-      <c r="BY3" s="99"/>
-      <c r="BZ3" s="99"/>
-      <c r="CA3" s="99">
+      <c r="BW3" s="86"/>
+      <c r="BX3" s="86"/>
+      <c r="BY3" s="86"/>
+      <c r="BZ3" s="86"/>
+      <c r="CA3" s="86">
         <f t="shared" ref="CA3" si="9">CA4</f>
         <v>45978</v>
       </c>
-      <c r="CB3" s="99"/>
-      <c r="CC3" s="99"/>
-      <c r="CD3" s="99"/>
-      <c r="CE3" s="99"/>
-      <c r="CF3" s="99">
+      <c r="CB3" s="86"/>
+      <c r="CC3" s="86"/>
+      <c r="CD3" s="86"/>
+      <c r="CE3" s="86"/>
+      <c r="CF3" s="86">
         <f t="shared" ref="CF3" si="10">CF4</f>
         <v>45985</v>
       </c>
-      <c r="CG3" s="99"/>
-      <c r="CH3" s="99"/>
-      <c r="CI3" s="99"/>
-      <c r="CJ3" s="99"/>
-      <c r="CK3" s="99">
+      <c r="CG3" s="86"/>
+      <c r="CH3" s="86"/>
+      <c r="CI3" s="86"/>
+      <c r="CJ3" s="86"/>
+      <c r="CK3" s="86">
         <f t="shared" ref="CK3" si="11">CK4</f>
         <v>45992</v>
       </c>
-      <c r="CL3" s="99"/>
-      <c r="CM3" s="99"/>
-      <c r="CN3" s="99"/>
-      <c r="CO3" s="100"/>
-      <c r="CP3" s="84"/>
-      <c r="CQ3" s="74"/>
-      <c r="CR3" s="74"/>
-      <c r="CS3" s="74"/>
-      <c r="CT3" s="74"/>
-      <c r="CU3" s="74"/>
-      <c r="CV3" s="74"/>
+      <c r="CL3" s="86"/>
+      <c r="CM3" s="86"/>
+      <c r="CN3" s="86"/>
+      <c r="CO3" s="87"/>
+      <c r="CP3" s="82"/>
+      <c r="CQ3" s="72"/>
+      <c r="CR3" s="72"/>
+      <c r="CS3" s="72"/>
+      <c r="CT3" s="72"/>
+      <c r="CU3" s="72"/>
+      <c r="CV3" s="72"/>
     </row>
     <row r="4" spans="1:121" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="I4" s="45">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="I4" s="44">
         <f t="shared" ref="I4:AN4" si="12">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(A1)-1)</f>
         <v>45880</v>
       </c>
-      <c r="J4" s="45">
+      <c r="J4" s="44">
         <f t="shared" si="12"/>
         <v>45881</v>
       </c>
-      <c r="K4" s="45">
+      <c r="K4" s="44">
         <f>WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(C1)-1)</f>
         <v>45882</v>
       </c>
-      <c r="L4" s="45">
+      <c r="L4" s="44">
         <f t="shared" si="12"/>
         <v>45883</v>
       </c>
-      <c r="M4" s="45">
+      <c r="M4" s="44">
         <f t="shared" si="12"/>
         <v>45884</v>
       </c>
-      <c r="N4" s="45">
+      <c r="N4" s="44">
         <f t="shared" si="12"/>
         <v>45887</v>
       </c>
-      <c r="O4" s="45">
+      <c r="O4" s="44">
         <f t="shared" si="12"/>
         <v>45888</v>
       </c>
-      <c r="P4" s="40">
+      <c r="P4" s="39">
         <f t="shared" si="12"/>
         <v>45889</v>
       </c>
-      <c r="Q4" s="40">
+      <c r="Q4" s="39">
         <f t="shared" si="12"/>
         <v>45890</v>
       </c>
-      <c r="R4" s="40">
+      <c r="R4" s="39">
         <f t="shared" si="12"/>
         <v>45891</v>
       </c>
-      <c r="S4" s="40">
+      <c r="S4" s="39">
         <f t="shared" si="12"/>
         <v>45894</v>
       </c>
-      <c r="T4" s="40">
+      <c r="T4" s="39">
         <f t="shared" si="12"/>
         <v>45895</v>
       </c>
-      <c r="U4" s="40">
+      <c r="U4" s="39">
         <f t="shared" si="12"/>
         <v>45896</v>
       </c>
-      <c r="V4" s="40">
+      <c r="V4" s="39">
         <f t="shared" si="12"/>
         <v>45897</v>
       </c>
-      <c r="W4" s="40">
+      <c r="W4" s="39">
         <f t="shared" si="12"/>
         <v>45898</v>
       </c>
-      <c r="X4" s="40">
+      <c r="X4" s="39">
         <f t="shared" si="12"/>
         <v>45901</v>
       </c>
-      <c r="Y4" s="40">
+      <c r="Y4" s="39">
         <f t="shared" si="12"/>
         <v>45902</v>
       </c>
-      <c r="Z4" s="40">
+      <c r="Z4" s="39">
         <f t="shared" si="12"/>
         <v>45903</v>
       </c>
-      <c r="AA4" s="40">
+      <c r="AA4" s="39">
         <f t="shared" si="12"/>
         <v>45904</v>
       </c>
-      <c r="AB4" s="40">
+      <c r="AB4" s="39">
         <f t="shared" si="12"/>
         <v>45905</v>
       </c>
-      <c r="AC4" s="40">
+      <c r="AC4" s="39">
         <f t="shared" si="12"/>
         <v>45908</v>
       </c>
-      <c r="AD4" s="40">
+      <c r="AD4" s="39">
         <f t="shared" si="12"/>
         <v>45909</v>
       </c>
-      <c r="AE4" s="40">
+      <c r="AE4" s="39">
         <f t="shared" si="12"/>
         <v>45910</v>
       </c>
-      <c r="AF4" s="40">
+      <c r="AF4" s="39">
         <f t="shared" si="12"/>
         <v>45911</v>
       </c>
-      <c r="AG4" s="40">
+      <c r="AG4" s="39">
         <f t="shared" si="12"/>
         <v>45912</v>
       </c>
-      <c r="AH4" s="40">
+      <c r="AH4" s="39">
         <f t="shared" si="12"/>
         <v>45915</v>
       </c>
-      <c r="AI4" s="40">
+      <c r="AI4" s="39">
         <f t="shared" si="12"/>
         <v>45916</v>
       </c>
-      <c r="AJ4" s="40">
+      <c r="AJ4" s="39">
         <f t="shared" si="12"/>
         <v>45917</v>
       </c>
-      <c r="AK4" s="40">
+      <c r="AK4" s="39">
         <f t="shared" si="12"/>
         <v>45918</v>
       </c>
-      <c r="AL4" s="40">
+      <c r="AL4" s="39">
         <f t="shared" si="12"/>
         <v>45919</v>
       </c>
-      <c r="AM4" s="40">
+      <c r="AM4" s="39">
         <f t="shared" si="12"/>
         <v>45922</v>
       </c>
-      <c r="AN4" s="40">
+      <c r="AN4" s="39">
         <f t="shared" si="12"/>
         <v>45923</v>
       </c>
-      <c r="AO4" s="40">
+      <c r="AO4" s="39">
         <f t="shared" ref="AO4:BT4" si="13">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(AG1)-1)</f>
         <v>45924</v>
       </c>
-      <c r="AP4" s="40">
+      <c r="AP4" s="39">
         <f t="shared" si="13"/>
         <v>45925</v>
       </c>
-      <c r="AQ4" s="40">
+      <c r="AQ4" s="39">
         <f t="shared" si="13"/>
         <v>45926</v>
       </c>
-      <c r="AR4" s="40">
+      <c r="AR4" s="39">
         <f t="shared" si="13"/>
         <v>45929</v>
       </c>
-      <c r="AS4" s="40">
+      <c r="AS4" s="39">
         <f t="shared" si="13"/>
         <v>45930</v>
       </c>
-      <c r="AT4" s="40">
+      <c r="AT4" s="39">
         <f t="shared" si="13"/>
         <v>45931</v>
       </c>
-      <c r="AU4" s="40">
+      <c r="AU4" s="39">
         <f t="shared" si="13"/>
         <v>45932</v>
       </c>
-      <c r="AV4" s="40">
+      <c r="AV4" s="39">
         <f t="shared" si="13"/>
         <v>45933</v>
       </c>
-      <c r="AW4" s="40">
+      <c r="AW4" s="39">
         <f t="shared" si="13"/>
         <v>45936</v>
       </c>
-      <c r="AX4" s="40">
+      <c r="AX4" s="39">
         <f t="shared" si="13"/>
         <v>45937</v>
       </c>
-      <c r="AY4" s="40">
+      <c r="AY4" s="39">
         <f t="shared" si="13"/>
         <v>45938</v>
       </c>
-      <c r="AZ4" s="40">
+      <c r="AZ4" s="39">
         <f t="shared" si="13"/>
         <v>45939</v>
       </c>
-      <c r="BA4" s="40">
+      <c r="BA4" s="39">
         <f t="shared" si="13"/>
         <v>45940</v>
       </c>
-      <c r="BB4" s="40">
+      <c r="BB4" s="39">
         <f t="shared" si="13"/>
         <v>45943</v>
       </c>
-      <c r="BC4" s="40">
+      <c r="BC4" s="39">
         <f t="shared" si="13"/>
         <v>45944</v>
       </c>
-      <c r="BD4" s="40">
+      <c r="BD4" s="39">
         <f t="shared" si="13"/>
         <v>45945</v>
       </c>
-      <c r="BE4" s="40">
+      <c r="BE4" s="39">
         <f t="shared" si="13"/>
         <v>45946</v>
       </c>
-      <c r="BF4" s="40">
+      <c r="BF4" s="39">
         <f t="shared" si="13"/>
         <v>45947</v>
       </c>
-      <c r="BG4" s="40">
+      <c r="BG4" s="39">
         <f t="shared" si="13"/>
         <v>45950</v>
       </c>
-      <c r="BH4" s="40">
+      <c r="BH4" s="39">
         <f t="shared" si="13"/>
         <v>45951</v>
       </c>
-      <c r="BI4" s="40">
+      <c r="BI4" s="39">
         <f t="shared" si="13"/>
         <v>45952</v>
       </c>
-      <c r="BJ4" s="40">
+      <c r="BJ4" s="39">
         <f t="shared" si="13"/>
         <v>45953</v>
       </c>
-      <c r="BK4" s="40">
+      <c r="BK4" s="39">
         <f t="shared" si="13"/>
         <v>45954</v>
       </c>
-      <c r="BL4" s="40">
+      <c r="BL4" s="39">
         <f t="shared" si="13"/>
         <v>45957</v>
       </c>
-      <c r="BM4" s="40">
+      <c r="BM4" s="39">
         <f t="shared" si="13"/>
         <v>45958</v>
       </c>
-      <c r="BN4" s="40">
+      <c r="BN4" s="39">
         <f t="shared" si="13"/>
         <v>45959</v>
       </c>
-      <c r="BO4" s="40">
+      <c r="BO4" s="39">
         <f t="shared" si="13"/>
         <v>45960</v>
       </c>
-      <c r="BP4" s="40">
+      <c r="BP4" s="39">
         <f t="shared" si="13"/>
         <v>45961</v>
       </c>
-      <c r="BQ4" s="40">
+      <c r="BQ4" s="39">
         <f t="shared" si="13"/>
         <v>45964</v>
       </c>
-      <c r="BR4" s="40">
+      <c r="BR4" s="39">
         <f t="shared" si="13"/>
         <v>45965</v>
       </c>
-      <c r="BS4" s="40">
+      <c r="BS4" s="39">
         <f t="shared" si="13"/>
         <v>45966</v>
       </c>
-      <c r="BT4" s="40">
+      <c r="BT4" s="39">
         <f t="shared" si="13"/>
         <v>45967</v>
       </c>
-      <c r="BU4" s="40">
+      <c r="BU4" s="39">
         <f t="shared" ref="BU4:CH4" si="14">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(BM1)-1)</f>
         <v>45968</v>
       </c>
-      <c r="BV4" s="40">
+      <c r="BV4" s="39">
         <f t="shared" si="14"/>
         <v>45971</v>
       </c>
-      <c r="BW4" s="40">
+      <c r="BW4" s="39">
         <f t="shared" si="14"/>
         <v>45972</v>
       </c>
-      <c r="BX4" s="40">
+      <c r="BX4" s="39">
         <f t="shared" si="14"/>
         <v>45973</v>
       </c>
-      <c r="BY4" s="40">
+      <c r="BY4" s="39">
         <f t="shared" si="14"/>
         <v>45974</v>
       </c>
-      <c r="BZ4" s="40">
+      <c r="BZ4" s="39">
         <f t="shared" si="14"/>
         <v>45975</v>
       </c>
-      <c r="CA4" s="40">
+      <c r="CA4" s="39">
         <f t="shared" si="14"/>
         <v>45978</v>
       </c>
-      <c r="CB4" s="40">
+      <c r="CB4" s="39">
         <f t="shared" si="14"/>
         <v>45979</v>
       </c>
-      <c r="CC4" s="40">
+      <c r="CC4" s="39">
         <f t="shared" si="14"/>
         <v>45980</v>
       </c>
-      <c r="CD4" s="40">
+      <c r="CD4" s="39">
         <f t="shared" si="14"/>
         <v>45981</v>
       </c>
-      <c r="CE4" s="40">
+      <c r="CE4" s="39">
         <f t="shared" si="14"/>
         <v>45982</v>
       </c>
-      <c r="CF4" s="40">
+      <c r="CF4" s="39">
         <f t="shared" si="14"/>
         <v>45985</v>
       </c>
-      <c r="CG4" s="72">
+      <c r="CG4" s="70">
         <f t="shared" si="14"/>
         <v>45986</v>
       </c>
-      <c r="CH4" s="72">
+      <c r="CH4" s="70">
         <f t="shared" si="14"/>
         <v>45987</v>
       </c>
-      <c r="CI4" s="72">
+      <c r="CI4" s="70">
         <f t="shared" ref="CI4" si="15">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(CA1)-1)</f>
         <v>45988</v>
       </c>
-      <c r="CJ4" s="72">
+      <c r="CJ4" s="70">
         <f t="shared" ref="CJ4" si="16">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(CB1)-1)</f>
         <v>45989</v>
       </c>
-      <c r="CK4" s="40">
+      <c r="CK4" s="39">
         <f t="shared" ref="CK4" si="17">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(CC1)-1)</f>
         <v>45992</v>
       </c>
-      <c r="CL4" s="40">
+      <c r="CL4" s="39">
         <f t="shared" ref="CL4" si="18">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(CD1)-1)</f>
         <v>45993</v>
       </c>
-      <c r="CM4" s="40">
+      <c r="CM4" s="39">
         <f t="shared" ref="CM4" si="19">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(CE1)-1)</f>
         <v>45994</v>
       </c>
-      <c r="CN4" s="40">
+      <c r="CN4" s="39">
         <f t="shared" ref="CN4" si="20">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(CF1)-1)</f>
         <v>45995</v>
       </c>
-      <c r="CO4" s="40">
+      <c r="CO4" s="39">
         <f t="shared" ref="CO4" si="21">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(CG1)-1)</f>
         <v>45996</v>
       </c>
-      <c r="CP4" s="85"/>
-      <c r="CQ4" s="75"/>
-      <c r="CR4" s="75"/>
-      <c r="CS4" s="75"/>
-      <c r="CT4" s="75"/>
-      <c r="CU4" s="75"/>
-      <c r="CV4" s="75"/>
+      <c r="CP4" s="83"/>
+      <c r="CQ4" s="73"/>
+      <c r="CR4" s="73"/>
+      <c r="CS4" s="73"/>
+      <c r="CT4" s="73"/>
+      <c r="CU4" s="73"/>
+      <c r="CV4" s="73"/>
     </row>
     <row r="5" spans="1:121" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
@@ -2889,369 +2883,369 @@
         <f t="shared" si="24"/>
         <v>l</v>
       </c>
-      <c r="CG5" s="71" t="str">
+      <c r="CG5" s="69" t="str">
         <f t="shared" si="24"/>
         <v>m</v>
       </c>
-      <c r="CH5" s="71" t="str">
+      <c r="CH5" s="69" t="str">
         <f t="shared" si="24"/>
         <v>m</v>
       </c>
-      <c r="CI5" s="71" t="str">
+      <c r="CI5" s="69" t="str">
         <f t="shared" si="24"/>
         <v>j</v>
       </c>
-      <c r="CJ5" s="71" t="str">
+      <c r="CJ5" s="69" t="str">
         <f t="shared" si="24"/>
         <v>v</v>
       </c>
-      <c r="CK5" s="71" t="str">
+      <c r="CK5" s="69" t="str">
         <f t="shared" si="24"/>
         <v>l</v>
       </c>
-      <c r="CL5" s="71" t="str">
+      <c r="CL5" s="69" t="str">
         <f t="shared" si="24"/>
         <v>m</v>
       </c>
-      <c r="CM5" s="71" t="str">
+      <c r="CM5" s="69" t="str">
         <f t="shared" si="24"/>
         <v>m</v>
       </c>
-      <c r="CN5" s="71" t="str">
+      <c r="CN5" s="69" t="str">
         <f t="shared" si="24"/>
         <v>j</v>
       </c>
-      <c r="CO5" s="82" t="str">
+      <c r="CO5" s="80" t="str">
         <f t="shared" si="24"/>
         <v>v</v>
       </c>
-      <c r="CP5" s="86"/>
+      <c r="CP5" s="84"/>
     </row>
     <row r="6" spans="1:121" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="26"/>
+      <c r="C6" s="25"/>
       <c r="E6"/>
-      <c r="H6" s="47" t="str">
+      <c r="H6" s="46" t="str">
         <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20"/>
-      <c r="V6" s="20"/>
-      <c r="W6" s="20"/>
-      <c r="X6" s="20"/>
-      <c r="Y6" s="20"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="20"/>
-      <c r="AC6" s="20"/>
-      <c r="AD6" s="20"/>
-      <c r="AE6" s="20"/>
-      <c r="AF6" s="20"/>
-      <c r="AG6" s="20"/>
-      <c r="AH6" s="20"/>
-      <c r="AI6" s="20"/>
-      <c r="AJ6" s="20"/>
-      <c r="AK6" s="20"/>
-      <c r="AL6" s="20"/>
-      <c r="AM6" s="20"/>
-      <c r="AN6" s="20"/>
-      <c r="AO6" s="20"/>
-      <c r="AP6" s="20"/>
-      <c r="AQ6" s="20"/>
-      <c r="AR6" s="20"/>
-      <c r="AS6" s="20"/>
-      <c r="AT6" s="20"/>
-      <c r="AU6" s="20"/>
-      <c r="AV6" s="20"/>
-      <c r="AW6" s="20"/>
-      <c r="AX6" s="20"/>
-      <c r="AY6" s="20"/>
-      <c r="AZ6" s="20"/>
-      <c r="BA6" s="20"/>
-      <c r="BB6" s="20"/>
-      <c r="BC6" s="20"/>
-      <c r="BD6" s="20"/>
-      <c r="BE6" s="20"/>
-      <c r="BF6" s="20"/>
-      <c r="BG6" s="20"/>
-      <c r="BH6" s="20"/>
-      <c r="BI6" s="20"/>
-      <c r="BJ6" s="20"/>
-      <c r="BK6" s="20"/>
-      <c r="BL6" s="20"/>
-      <c r="BM6" s="20"/>
-      <c r="BN6" s="20"/>
-      <c r="BO6" s="20"/>
-      <c r="BP6" s="20"/>
-      <c r="BQ6" s="20"/>
-      <c r="BR6" s="20"/>
-      <c r="BS6" s="20"/>
-      <c r="BT6" s="20"/>
-      <c r="BU6" s="20"/>
-      <c r="BV6" s="20"/>
-      <c r="BW6" s="20"/>
-      <c r="BX6" s="20"/>
-      <c r="BY6" s="20"/>
-      <c r="BZ6" s="20"/>
-      <c r="CA6" s="20"/>
-      <c r="CB6" s="20"/>
-      <c r="CC6" s="20"/>
-      <c r="CD6" s="20"/>
-      <c r="CE6" s="20"/>
-      <c r="CF6" s="20"/>
-      <c r="CG6" s="20"/>
-      <c r="CP6" s="86"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="19"/>
+      <c r="AG6" s="19"/>
+      <c r="AH6" s="19"/>
+      <c r="AI6" s="19"/>
+      <c r="AJ6" s="19"/>
+      <c r="AK6" s="19"/>
+      <c r="AL6" s="19"/>
+      <c r="AM6" s="19"/>
+      <c r="AN6" s="19"/>
+      <c r="AO6" s="19"/>
+      <c r="AP6" s="19"/>
+      <c r="AQ6" s="19"/>
+      <c r="AR6" s="19"/>
+      <c r="AS6" s="19"/>
+      <c r="AT6" s="19"/>
+      <c r="AU6" s="19"/>
+      <c r="AV6" s="19"/>
+      <c r="AW6" s="19"/>
+      <c r="AX6" s="19"/>
+      <c r="AY6" s="19"/>
+      <c r="AZ6" s="19"/>
+      <c r="BA6" s="19"/>
+      <c r="BB6" s="19"/>
+      <c r="BC6" s="19"/>
+      <c r="BD6" s="19"/>
+      <c r="BE6" s="19"/>
+      <c r="BF6" s="19"/>
+      <c r="BG6" s="19"/>
+      <c r="BH6" s="19"/>
+      <c r="BI6" s="19"/>
+      <c r="BJ6" s="19"/>
+      <c r="BK6" s="19"/>
+      <c r="BL6" s="19"/>
+      <c r="BM6" s="19"/>
+      <c r="BN6" s="19"/>
+      <c r="BO6" s="19"/>
+      <c r="BP6" s="19"/>
+      <c r="BQ6" s="19"/>
+      <c r="BR6" s="19"/>
+      <c r="BS6" s="19"/>
+      <c r="BT6" s="19"/>
+      <c r="BU6" s="19"/>
+      <c r="BV6" s="19"/>
+      <c r="BW6" s="19"/>
+      <c r="BX6" s="19"/>
+      <c r="BY6" s="19"/>
+      <c r="BZ6" s="19"/>
+      <c r="CA6" s="19"/>
+      <c r="CB6" s="19"/>
+      <c r="CC6" s="19"/>
+      <c r="CD6" s="19"/>
+      <c r="CE6" s="19"/>
+      <c r="CF6" s="19"/>
+      <c r="CG6" s="19"/>
+      <c r="CP6" s="84"/>
     </row>
-    <row r="7" spans="1:121" s="79" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54" t="s">
+    <row r="7" spans="1:121" s="77" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="52"/>
+      <c r="B7" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59" t="str">
+      <c r="C7" s="54"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58" t="str">
         <f t="shared" ref="H7:H28" si="25">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I7" s="101"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="102"/>
-      <c r="Q7" s="102"/>
-      <c r="R7" s="102"/>
-      <c r="S7" s="102"/>
-      <c r="T7" s="102"/>
-      <c r="U7" s="102"/>
-      <c r="V7" s="102"/>
-      <c r="W7" s="102"/>
-      <c r="X7" s="102"/>
-      <c r="Y7" s="102"/>
-      <c r="Z7" s="102"/>
-      <c r="AA7" s="102"/>
-      <c r="AB7" s="102"/>
-      <c r="AC7" s="102"/>
-      <c r="AD7" s="102"/>
-      <c r="AE7" s="102"/>
-      <c r="AF7" s="102"/>
-      <c r="AG7" s="102"/>
-      <c r="AH7" s="102"/>
-      <c r="AI7" s="102"/>
-      <c r="AJ7" s="102"/>
-      <c r="AK7" s="102"/>
-      <c r="AL7" s="102"/>
-      <c r="AM7" s="102"/>
-      <c r="AN7" s="102"/>
-      <c r="AO7" s="102"/>
-      <c r="AP7" s="102"/>
-      <c r="AQ7" s="102"/>
-      <c r="AR7" s="102"/>
-      <c r="AS7" s="102"/>
-      <c r="AT7" s="102"/>
-      <c r="AU7" s="102"/>
-      <c r="AV7" s="102"/>
-      <c r="AW7" s="102"/>
-      <c r="AX7" s="102"/>
-      <c r="AY7" s="102"/>
-      <c r="AZ7" s="102"/>
-      <c r="BA7" s="102"/>
-      <c r="BB7" s="102"/>
-      <c r="BC7" s="102"/>
-      <c r="BD7" s="102"/>
-      <c r="BE7" s="102"/>
-      <c r="BF7" s="102"/>
-      <c r="BG7" s="102"/>
-      <c r="BH7" s="102"/>
-      <c r="BI7" s="102"/>
-      <c r="BJ7" s="102"/>
-      <c r="BK7" s="102"/>
-      <c r="BL7" s="102"/>
-      <c r="BM7" s="102"/>
-      <c r="BN7" s="102"/>
-      <c r="BO7" s="102"/>
-      <c r="BP7" s="102"/>
-      <c r="BQ7" s="102"/>
-      <c r="BR7" s="102"/>
-      <c r="BS7" s="102"/>
-      <c r="BT7" s="102"/>
-      <c r="BU7" s="102"/>
-      <c r="BV7" s="102"/>
-      <c r="BW7" s="102"/>
-      <c r="BX7" s="102"/>
-      <c r="BY7" s="102"/>
-      <c r="BZ7" s="102"/>
-      <c r="CA7" s="102"/>
-      <c r="CB7" s="102"/>
-      <c r="CC7" s="102"/>
-      <c r="CD7" s="102"/>
-      <c r="CE7" s="102"/>
-      <c r="CF7" s="102"/>
-      <c r="CG7" s="102"/>
-      <c r="CH7" s="102"/>
-      <c r="CI7" s="102"/>
-      <c r="CJ7" s="102"/>
-      <c r="CK7" s="102"/>
-      <c r="CL7" s="102"/>
-      <c r="CM7" s="102"/>
-      <c r="CN7" s="102"/>
-      <c r="CO7" s="102"/>
-      <c r="CP7" s="87"/>
-      <c r="CQ7" s="78"/>
-      <c r="CR7" s="78"/>
-      <c r="CS7" s="78"/>
-      <c r="CT7" s="78"/>
-      <c r="CU7" s="78"/>
-      <c r="CV7" s="78"/>
-      <c r="CW7" s="78"/>
-      <c r="CX7" s="78"/>
-      <c r="CY7" s="78"/>
-      <c r="CZ7" s="78"/>
-      <c r="DA7" s="78"/>
-      <c r="DB7" s="78"/>
-      <c r="DC7" s="78"/>
-      <c r="DD7" s="78"/>
-      <c r="DE7" s="78"/>
-      <c r="DF7" s="78"/>
-      <c r="DG7" s="78"/>
-      <c r="DH7" s="78"/>
-      <c r="DI7" s="78"/>
-      <c r="DJ7" s="78"/>
-      <c r="DK7" s="78"/>
-      <c r="DL7" s="78"/>
-      <c r="DM7" s="78"/>
-      <c r="DN7" s="78"/>
-      <c r="DO7" s="78"/>
-      <c r="DP7" s="78"/>
-      <c r="DQ7" s="78"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="89"/>
+      <c r="K7" s="89"/>
+      <c r="L7" s="89"/>
+      <c r="M7" s="89"/>
+      <c r="N7" s="89"/>
+      <c r="O7" s="89"/>
+      <c r="P7" s="89"/>
+      <c r="Q7" s="89"/>
+      <c r="R7" s="89"/>
+      <c r="S7" s="89"/>
+      <c r="T7" s="89"/>
+      <c r="U7" s="89"/>
+      <c r="V7" s="89"/>
+      <c r="W7" s="89"/>
+      <c r="X7" s="89"/>
+      <c r="Y7" s="89"/>
+      <c r="Z7" s="89"/>
+      <c r="AA7" s="89"/>
+      <c r="AB7" s="89"/>
+      <c r="AC7" s="89"/>
+      <c r="AD7" s="89"/>
+      <c r="AE7" s="89"/>
+      <c r="AF7" s="89"/>
+      <c r="AG7" s="89"/>
+      <c r="AH7" s="89"/>
+      <c r="AI7" s="89"/>
+      <c r="AJ7" s="89"/>
+      <c r="AK7" s="89"/>
+      <c r="AL7" s="89"/>
+      <c r="AM7" s="89"/>
+      <c r="AN7" s="89"/>
+      <c r="AO7" s="89"/>
+      <c r="AP7" s="89"/>
+      <c r="AQ7" s="89"/>
+      <c r="AR7" s="89"/>
+      <c r="AS7" s="89"/>
+      <c r="AT7" s="89"/>
+      <c r="AU7" s="89"/>
+      <c r="AV7" s="89"/>
+      <c r="AW7" s="89"/>
+      <c r="AX7" s="89"/>
+      <c r="AY7" s="89"/>
+      <c r="AZ7" s="89"/>
+      <c r="BA7" s="89"/>
+      <c r="BB7" s="89"/>
+      <c r="BC7" s="89"/>
+      <c r="BD7" s="89"/>
+      <c r="BE7" s="89"/>
+      <c r="BF7" s="89"/>
+      <c r="BG7" s="89"/>
+      <c r="BH7" s="89"/>
+      <c r="BI7" s="89"/>
+      <c r="BJ7" s="89"/>
+      <c r="BK7" s="89"/>
+      <c r="BL7" s="89"/>
+      <c r="BM7" s="89"/>
+      <c r="BN7" s="89"/>
+      <c r="BO7" s="89"/>
+      <c r="BP7" s="89"/>
+      <c r="BQ7" s="89"/>
+      <c r="BR7" s="89"/>
+      <c r="BS7" s="89"/>
+      <c r="BT7" s="89"/>
+      <c r="BU7" s="89"/>
+      <c r="BV7" s="89"/>
+      <c r="BW7" s="89"/>
+      <c r="BX7" s="89"/>
+      <c r="BY7" s="89"/>
+      <c r="BZ7" s="89"/>
+      <c r="CA7" s="89"/>
+      <c r="CB7" s="89"/>
+      <c r="CC7" s="89"/>
+      <c r="CD7" s="89"/>
+      <c r="CE7" s="89"/>
+      <c r="CF7" s="89"/>
+      <c r="CG7" s="89"/>
+      <c r="CH7" s="89"/>
+      <c r="CI7" s="89"/>
+      <c r="CJ7" s="89"/>
+      <c r="CK7" s="89"/>
+      <c r="CL7" s="89"/>
+      <c r="CM7" s="89"/>
+      <c r="CN7" s="89"/>
+      <c r="CO7" s="89"/>
+      <c r="CP7" s="85"/>
+      <c r="CQ7" s="76"/>
+      <c r="CR7" s="76"/>
+      <c r="CS7" s="76"/>
+      <c r="CT7" s="76"/>
+      <c r="CU7" s="76"/>
+      <c r="CV7" s="76"/>
+      <c r="CW7" s="76"/>
+      <c r="CX7" s="76"/>
+      <c r="CY7" s="76"/>
+      <c r="CZ7" s="76"/>
+      <c r="DA7" s="76"/>
+      <c r="DB7" s="76"/>
+      <c r="DC7" s="76"/>
+      <c r="DD7" s="76"/>
+      <c r="DE7" s="76"/>
+      <c r="DF7" s="76"/>
+      <c r="DG7" s="76"/>
+      <c r="DH7" s="76"/>
+      <c r="DI7" s="76"/>
+      <c r="DJ7" s="76"/>
+      <c r="DK7" s="76"/>
+      <c r="DL7" s="76"/>
+      <c r="DM7" s="76"/>
+      <c r="DN7" s="76"/>
+      <c r="DO7" s="76"/>
+      <c r="DP7" s="76"/>
+      <c r="DQ7" s="76"/>
     </row>
     <row r="8" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="98"/>
+      <c r="C8" s="100"/>
       <c r="D8" s="13">
         <v>1</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="40">
         <v>45884</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="40">
         <v>45891</v>
       </c>
-      <c r="G8" s="48"/>
+      <c r="G8" s="47"/>
       <c r="H8" s="12">
         <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>8</v>
       </c>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="21"/>
-      <c r="V8" s="21"/>
-      <c r="W8" s="20"/>
-      <c r="X8" s="20"/>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="20"/>
-      <c r="AD8" s="20"/>
-      <c r="AE8" s="20"/>
-      <c r="AF8" s="20"/>
-      <c r="AG8" s="20"/>
-      <c r="AH8" s="20"/>
-      <c r="AI8" s="20"/>
-      <c r="AJ8" s="20"/>
-      <c r="AK8" s="80"/>
-      <c r="AL8" s="80"/>
-      <c r="AM8" s="20"/>
-      <c r="AN8" s="20"/>
-      <c r="AO8" s="20"/>
-      <c r="AP8" s="20"/>
-      <c r="AQ8" s="20"/>
-      <c r="AR8" s="20"/>
-      <c r="AS8" s="20"/>
-      <c r="AT8" s="20"/>
-      <c r="AU8" s="20"/>
-      <c r="AV8" s="20"/>
-      <c r="AW8" s="20"/>
-      <c r="AX8" s="20"/>
-      <c r="AY8" s="20"/>
-      <c r="AZ8" s="20"/>
-      <c r="BA8" s="20"/>
-      <c r="BB8" s="20"/>
-      <c r="BC8" s="20"/>
-      <c r="BD8" s="20"/>
-      <c r="BE8" s="20"/>
-      <c r="BF8" s="20"/>
-      <c r="BG8" s="20"/>
-      <c r="BH8" s="43"/>
-      <c r="BI8" s="20"/>
-      <c r="BJ8" s="20"/>
-      <c r="BK8" s="20"/>
-      <c r="BL8" s="20"/>
-      <c r="BM8" s="20"/>
-      <c r="BN8" s="20"/>
-      <c r="BO8" s="20"/>
-      <c r="BP8" s="80"/>
-      <c r="BQ8" s="43"/>
-      <c r="BR8" s="43"/>
-      <c r="BS8" s="43"/>
-      <c r="BT8" s="43"/>
-      <c r="BU8" s="43"/>
-      <c r="BV8" s="43"/>
-      <c r="BW8" s="43"/>
-      <c r="BX8" s="43"/>
-      <c r="BY8" s="44"/>
-      <c r="BZ8" s="44"/>
-      <c r="CA8" s="43"/>
-      <c r="CB8" s="43"/>
-      <c r="CC8" s="43"/>
-      <c r="CD8" s="43"/>
-      <c r="CE8" s="43"/>
-      <c r="CF8" s="43"/>
-      <c r="CG8" s="76"/>
-      <c r="CH8" s="43"/>
-      <c r="CI8" s="76"/>
-      <c r="CJ8" s="76"/>
-      <c r="CK8" s="76"/>
-      <c r="CL8" s="76"/>
-      <c r="CM8" s="76"/>
-      <c r="CN8" s="76"/>
-      <c r="CO8" s="76"/>
-      <c r="CP8" s="86"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="19"/>
+      <c r="X8" s="19"/>
+      <c r="Y8" s="19"/>
+      <c r="Z8" s="19"/>
+      <c r="AA8" s="19"/>
+      <c r="AB8" s="19"/>
+      <c r="AC8" s="19"/>
+      <c r="AD8" s="19"/>
+      <c r="AE8" s="19"/>
+      <c r="AF8" s="19"/>
+      <c r="AG8" s="19"/>
+      <c r="AH8" s="19"/>
+      <c r="AI8" s="19"/>
+      <c r="AJ8" s="19"/>
+      <c r="AK8" s="78"/>
+      <c r="AL8" s="78"/>
+      <c r="AM8" s="19"/>
+      <c r="AN8" s="19"/>
+      <c r="AO8" s="19"/>
+      <c r="AP8" s="19"/>
+      <c r="AQ8" s="19"/>
+      <c r="AR8" s="19"/>
+      <c r="AS8" s="19"/>
+      <c r="AT8" s="19"/>
+      <c r="AU8" s="19"/>
+      <c r="AV8" s="19"/>
+      <c r="AW8" s="19"/>
+      <c r="AX8" s="19"/>
+      <c r="AY8" s="19"/>
+      <c r="AZ8" s="19"/>
+      <c r="BA8" s="19"/>
+      <c r="BB8" s="19"/>
+      <c r="BC8" s="19"/>
+      <c r="BD8" s="19"/>
+      <c r="BE8" s="19"/>
+      <c r="BF8" s="19"/>
+      <c r="BG8" s="19"/>
+      <c r="BH8" s="42"/>
+      <c r="BI8" s="19"/>
+      <c r="BJ8" s="19"/>
+      <c r="BK8" s="19"/>
+      <c r="BL8" s="19"/>
+      <c r="BM8" s="19"/>
+      <c r="BN8" s="19"/>
+      <c r="BO8" s="19"/>
+      <c r="BP8" s="78"/>
+      <c r="BQ8" s="42"/>
+      <c r="BR8" s="42"/>
+      <c r="BS8" s="42"/>
+      <c r="BT8" s="42"/>
+      <c r="BU8" s="42"/>
+      <c r="BV8" s="42"/>
+      <c r="BW8" s="42"/>
+      <c r="BX8" s="42"/>
+      <c r="BY8" s="43"/>
+      <c r="BZ8" s="43"/>
+      <c r="CA8" s="42"/>
+      <c r="CB8" s="42"/>
+      <c r="CC8" s="42"/>
+      <c r="CD8" s="42"/>
+      <c r="CE8" s="42"/>
+      <c r="CF8" s="42"/>
+      <c r="CG8" s="74"/>
+      <c r="CH8" s="42"/>
+      <c r="CI8" s="74"/>
+      <c r="CJ8" s="74"/>
+      <c r="CK8" s="74"/>
+      <c r="CL8" s="74"/>
+      <c r="CM8" s="74"/>
+      <c r="CN8" s="74"/>
+      <c r="CO8" s="74"/>
+      <c r="CP8" s="84"/>
       <c r="CQ8"/>
       <c r="CR8"/>
       <c r="CS8"/>
@@ -3281,108 +3275,108 @@
       <c r="DQ8"/>
     </row>
     <row r="9" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="98" t="s">
+      <c r="A9" s="23"/>
+      <c r="B9" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="98"/>
+      <c r="C9" s="100"/>
       <c r="D9" s="13">
         <v>1</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="40">
         <v>45894</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="40">
         <v>45901</v>
       </c>
-      <c r="G9" s="48"/>
+      <c r="G9" s="47"/>
       <c r="H9" s="12"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="21"/>
-      <c r="V9" s="21"/>
-      <c r="W9" s="20"/>
-      <c r="X9" s="20"/>
-      <c r="Y9" s="20"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="20"/>
-      <c r="AC9" s="20"/>
-      <c r="AD9" s="20"/>
-      <c r="AE9" s="20"/>
-      <c r="AF9" s="20"/>
-      <c r="AG9" s="20"/>
-      <c r="AH9" s="20"/>
-      <c r="AI9" s="20"/>
-      <c r="AJ9" s="20"/>
-      <c r="AK9" s="80"/>
-      <c r="AL9" s="80"/>
-      <c r="AM9" s="20"/>
-      <c r="AN9" s="20"/>
-      <c r="AO9" s="20"/>
-      <c r="AP9" s="20"/>
-      <c r="AQ9" s="20"/>
-      <c r="AR9" s="20"/>
-      <c r="AS9" s="20"/>
-      <c r="AT9" s="20"/>
-      <c r="AU9" s="20"/>
-      <c r="AV9" s="20"/>
-      <c r="AW9" s="20"/>
-      <c r="AX9" s="20"/>
-      <c r="AY9" s="20"/>
-      <c r="AZ9" s="20"/>
-      <c r="BA9" s="20"/>
-      <c r="BB9" s="20"/>
-      <c r="BC9" s="20"/>
-      <c r="BD9" s="20"/>
-      <c r="BE9" s="20"/>
-      <c r="BF9" s="20"/>
-      <c r="BG9" s="20"/>
-      <c r="BH9" s="43"/>
-      <c r="BI9" s="20"/>
-      <c r="BJ9" s="20"/>
-      <c r="BK9" s="20"/>
-      <c r="BL9" s="20"/>
-      <c r="BM9" s="20"/>
-      <c r="BN9" s="20"/>
-      <c r="BO9" s="20"/>
-      <c r="BP9" s="80"/>
-      <c r="BQ9" s="43"/>
-      <c r="BR9" s="43"/>
-      <c r="BS9" s="43"/>
-      <c r="BT9" s="43"/>
-      <c r="BU9" s="43"/>
-      <c r="BV9" s="43"/>
-      <c r="BW9" s="43"/>
-      <c r="BX9" s="43"/>
-      <c r="BY9" s="44"/>
-      <c r="BZ9" s="44"/>
-      <c r="CA9" s="43"/>
-      <c r="CB9" s="43"/>
-      <c r="CC9" s="43"/>
-      <c r="CD9" s="43"/>
-      <c r="CE9" s="43"/>
-      <c r="CF9" s="43"/>
-      <c r="CG9" s="76"/>
-      <c r="CH9" s="43"/>
-      <c r="CI9" s="76"/>
-      <c r="CJ9" s="76"/>
-      <c r="CK9" s="76"/>
-      <c r="CL9" s="76"/>
-      <c r="CM9" s="76"/>
-      <c r="CN9" s="76"/>
-      <c r="CO9" s="76"/>
-      <c r="CP9" s="86"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="19"/>
+      <c r="AA9" s="19"/>
+      <c r="AB9" s="19"/>
+      <c r="AC9" s="19"/>
+      <c r="AD9" s="19"/>
+      <c r="AE9" s="19"/>
+      <c r="AF9" s="19"/>
+      <c r="AG9" s="19"/>
+      <c r="AH9" s="19"/>
+      <c r="AI9" s="19"/>
+      <c r="AJ9" s="19"/>
+      <c r="AK9" s="78"/>
+      <c r="AL9" s="78"/>
+      <c r="AM9" s="19"/>
+      <c r="AN9" s="19"/>
+      <c r="AO9" s="19"/>
+      <c r="AP9" s="19"/>
+      <c r="AQ9" s="19"/>
+      <c r="AR9" s="19"/>
+      <c r="AS9" s="19"/>
+      <c r="AT9" s="19"/>
+      <c r="AU9" s="19"/>
+      <c r="AV9" s="19"/>
+      <c r="AW9" s="19"/>
+      <c r="AX9" s="19"/>
+      <c r="AY9" s="19"/>
+      <c r="AZ9" s="19"/>
+      <c r="BA9" s="19"/>
+      <c r="BB9" s="19"/>
+      <c r="BC9" s="19"/>
+      <c r="BD9" s="19"/>
+      <c r="BE9" s="19"/>
+      <c r="BF9" s="19"/>
+      <c r="BG9" s="19"/>
+      <c r="BH9" s="42"/>
+      <c r="BI9" s="19"/>
+      <c r="BJ9" s="19"/>
+      <c r="BK9" s="19"/>
+      <c r="BL9" s="19"/>
+      <c r="BM9" s="19"/>
+      <c r="BN9" s="19"/>
+      <c r="BO9" s="19"/>
+      <c r="BP9" s="78"/>
+      <c r="BQ9" s="42"/>
+      <c r="BR9" s="42"/>
+      <c r="BS9" s="42"/>
+      <c r="BT9" s="42"/>
+      <c r="BU9" s="42"/>
+      <c r="BV9" s="42"/>
+      <c r="BW9" s="42"/>
+      <c r="BX9" s="42"/>
+      <c r="BY9" s="43"/>
+      <c r="BZ9" s="43"/>
+      <c r="CA9" s="42"/>
+      <c r="CB9" s="42"/>
+      <c r="CC9" s="42"/>
+      <c r="CD9" s="42"/>
+      <c r="CE9" s="42"/>
+      <c r="CF9" s="42"/>
+      <c r="CG9" s="74"/>
+      <c r="CH9" s="42"/>
+      <c r="CI9" s="74"/>
+      <c r="CJ9" s="74"/>
+      <c r="CK9" s="74"/>
+      <c r="CL9" s="74"/>
+      <c r="CM9" s="74"/>
+      <c r="CN9" s="74"/>
+      <c r="CO9" s="74"/>
+      <c r="CP9" s="84"/>
       <c r="CQ9"/>
       <c r="CR9"/>
       <c r="CS9"/>
@@ -3412,111 +3406,111 @@
       <c r="DQ9"/>
     </row>
     <row r="10" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23"/>
-      <c r="B10" s="98" t="s">
+      <c r="A10" s="22"/>
+      <c r="B10" s="100" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="98"/>
+      <c r="C10" s="100"/>
       <c r="D10" s="13">
         <v>1</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="40">
         <v>45896</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="40">
         <f>E10+7</f>
         <v>45903</v>
       </c>
-      <c r="G10" s="48"/>
+      <c r="G10" s="47"/>
       <c r="H10" s="12">
         <f t="shared" si="25"/>
         <v>8</v>
       </c>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="20"/>
-      <c r="V10" s="20"/>
-      <c r="W10" s="20"/>
-      <c r="X10" s="20"/>
-      <c r="Y10" s="20"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="20"/>
-      <c r="AB10" s="20"/>
-      <c r="AC10" s="20"/>
-      <c r="AD10" s="20"/>
-      <c r="AE10" s="20"/>
-      <c r="AF10" s="20"/>
-      <c r="AG10" s="20"/>
-      <c r="AH10" s="20"/>
-      <c r="AI10" s="20"/>
-      <c r="AJ10" s="20"/>
-      <c r="AK10" s="80"/>
-      <c r="AL10" s="80"/>
-      <c r="AM10" s="20"/>
-      <c r="AN10" s="20"/>
-      <c r="AO10" s="20"/>
-      <c r="AP10" s="20"/>
-      <c r="AQ10" s="20"/>
-      <c r="AR10" s="20"/>
-      <c r="AS10" s="20"/>
-      <c r="AT10" s="20"/>
-      <c r="AU10" s="20"/>
-      <c r="AV10" s="20"/>
-      <c r="AW10" s="20"/>
-      <c r="AX10" s="20"/>
-      <c r="AY10" s="20"/>
-      <c r="AZ10" s="20"/>
-      <c r="BA10" s="20"/>
-      <c r="BB10" s="20"/>
-      <c r="BC10" s="20"/>
-      <c r="BD10" s="20"/>
-      <c r="BE10" s="20"/>
-      <c r="BF10" s="20"/>
-      <c r="BG10" s="20"/>
-      <c r="BH10" s="43"/>
-      <c r="BI10" s="20"/>
-      <c r="BJ10" s="20"/>
-      <c r="BK10" s="20"/>
-      <c r="BL10" s="20"/>
-      <c r="BM10" s="20"/>
-      <c r="BN10" s="20"/>
-      <c r="BO10" s="20"/>
-      <c r="BP10" s="80"/>
-      <c r="BQ10" s="43"/>
-      <c r="BR10" s="43"/>
-      <c r="BS10" s="43"/>
-      <c r="BT10" s="43"/>
-      <c r="BU10" s="43"/>
-      <c r="BV10" s="43"/>
-      <c r="BW10" s="43"/>
-      <c r="BX10" s="43"/>
-      <c r="BY10" s="43"/>
-      <c r="BZ10" s="43"/>
-      <c r="CA10" s="43"/>
-      <c r="CB10" s="43"/>
-      <c r="CC10" s="43"/>
-      <c r="CD10" s="43"/>
-      <c r="CE10" s="43"/>
-      <c r="CF10" s="43"/>
-      <c r="CG10" s="76"/>
-      <c r="CH10" s="43"/>
-      <c r="CJ10" s="76"/>
-      <c r="CK10" s="76"/>
-      <c r="CL10" s="76"/>
-      <c r="CM10" s="76"/>
-      <c r="CN10" s="76"/>
-      <c r="CO10" s="76"/>
-      <c r="CP10" s="86"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="19"/>
+      <c r="AA10" s="19"/>
+      <c r="AB10" s="19"/>
+      <c r="AC10" s="19"/>
+      <c r="AD10" s="19"/>
+      <c r="AE10" s="19"/>
+      <c r="AF10" s="19"/>
+      <c r="AG10" s="19"/>
+      <c r="AH10" s="19"/>
+      <c r="AI10" s="19"/>
+      <c r="AJ10" s="19"/>
+      <c r="AK10" s="78"/>
+      <c r="AL10" s="78"/>
+      <c r="AM10" s="19"/>
+      <c r="AN10" s="19"/>
+      <c r="AO10" s="19"/>
+      <c r="AP10" s="19"/>
+      <c r="AQ10" s="19"/>
+      <c r="AR10" s="19"/>
+      <c r="AS10" s="19"/>
+      <c r="AT10" s="19"/>
+      <c r="AU10" s="19"/>
+      <c r="AV10" s="19"/>
+      <c r="AW10" s="19"/>
+      <c r="AX10" s="19"/>
+      <c r="AY10" s="19"/>
+      <c r="AZ10" s="19"/>
+      <c r="BA10" s="19"/>
+      <c r="BB10" s="19"/>
+      <c r="BC10" s="19"/>
+      <c r="BD10" s="19"/>
+      <c r="BE10" s="19"/>
+      <c r="BF10" s="19"/>
+      <c r="BG10" s="19"/>
+      <c r="BH10" s="42"/>
+      <c r="BI10" s="19"/>
+      <c r="BJ10" s="19"/>
+      <c r="BK10" s="19"/>
+      <c r="BL10" s="19"/>
+      <c r="BM10" s="19"/>
+      <c r="BN10" s="19"/>
+      <c r="BO10" s="19"/>
+      <c r="BP10" s="78"/>
+      <c r="BQ10" s="42"/>
+      <c r="BR10" s="42"/>
+      <c r="BS10" s="42"/>
+      <c r="BT10" s="42"/>
+      <c r="BU10" s="42"/>
+      <c r="BV10" s="42"/>
+      <c r="BW10" s="42"/>
+      <c r="BX10" s="42"/>
+      <c r="BY10" s="42"/>
+      <c r="BZ10" s="42"/>
+      <c r="CA10" s="42"/>
+      <c r="CB10" s="42"/>
+      <c r="CC10" s="42"/>
+      <c r="CD10" s="42"/>
+      <c r="CE10" s="42"/>
+      <c r="CF10" s="42"/>
+      <c r="CG10" s="74"/>
+      <c r="CH10" s="42"/>
+      <c r="CJ10" s="74"/>
+      <c r="CK10" s="74"/>
+      <c r="CL10" s="74"/>
+      <c r="CM10" s="74"/>
+      <c r="CN10" s="74"/>
+      <c r="CO10" s="74"/>
+      <c r="CP10" s="84"/>
       <c r="CQ10"/>
       <c r="CR10"/>
       <c r="CS10"/>
@@ -3546,108 +3540,108 @@
       <c r="DQ10"/>
     </row>
     <row r="11" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23"/>
-      <c r="B11" s="98" t="s">
+      <c r="A11" s="22"/>
+      <c r="B11" s="100" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="98"/>
+      <c r="C11" s="100"/>
       <c r="D11" s="13">
         <v>1</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="40">
         <v>45904</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="40">
         <v>45908</v>
       </c>
-      <c r="G11" s="48"/>
+      <c r="G11" s="47"/>
       <c r="H11" s="12"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="20"/>
-      <c r="U11" s="20"/>
-      <c r="V11" s="20"/>
-      <c r="W11" s="20"/>
-      <c r="X11" s="20"/>
-      <c r="Y11" s="20"/>
-      <c r="Z11" s="20"/>
-      <c r="AA11" s="20"/>
-      <c r="AB11" s="20"/>
-      <c r="AC11" s="20"/>
-      <c r="AD11" s="20"/>
-      <c r="AE11" s="20"/>
-      <c r="AF11" s="20"/>
-      <c r="AG11" s="20"/>
-      <c r="AH11" s="20"/>
-      <c r="AI11" s="20"/>
-      <c r="AJ11" s="20"/>
-      <c r="AK11" s="80"/>
-      <c r="AL11" s="80"/>
-      <c r="AM11" s="20"/>
-      <c r="AN11" s="20"/>
-      <c r="AO11" s="20"/>
-      <c r="AP11" s="20"/>
-      <c r="AQ11" s="20"/>
-      <c r="AR11" s="20"/>
-      <c r="AS11" s="20"/>
-      <c r="AT11" s="20"/>
-      <c r="AU11" s="20"/>
-      <c r="AV11" s="20"/>
-      <c r="AW11" s="20"/>
-      <c r="AX11" s="20"/>
-      <c r="AY11" s="20"/>
-      <c r="AZ11" s="20"/>
-      <c r="BA11" s="20"/>
-      <c r="BB11" s="20"/>
-      <c r="BC11" s="20"/>
-      <c r="BD11" s="20"/>
-      <c r="BE11" s="20"/>
-      <c r="BF11" s="20"/>
-      <c r="BG11" s="20"/>
-      <c r="BH11" s="43"/>
-      <c r="BI11" s="20"/>
-      <c r="BJ11" s="20"/>
-      <c r="BK11" s="20"/>
-      <c r="BL11" s="20"/>
-      <c r="BM11" s="20"/>
-      <c r="BN11" s="20"/>
-      <c r="BO11" s="20"/>
-      <c r="BP11" s="80"/>
-      <c r="BQ11" s="43"/>
-      <c r="BR11" s="43"/>
-      <c r="BS11" s="43"/>
-      <c r="BT11" s="43"/>
-      <c r="BU11" s="43"/>
-      <c r="BV11" s="43"/>
-      <c r="BW11" s="43"/>
-      <c r="BX11" s="43"/>
-      <c r="BY11" s="43"/>
-      <c r="BZ11" s="43"/>
-      <c r="CA11" s="43"/>
-      <c r="CB11" s="43"/>
-      <c r="CC11" s="43"/>
-      <c r="CD11" s="43"/>
-      <c r="CE11" s="43"/>
-      <c r="CF11" s="43"/>
-      <c r="CG11" s="76"/>
-      <c r="CH11" s="43"/>
-      <c r="CI11" s="76"/>
-      <c r="CJ11" s="76"/>
-      <c r="CK11" s="76"/>
-      <c r="CL11" s="76"/>
-      <c r="CM11" s="76"/>
-      <c r="CN11" s="76"/>
-      <c r="CO11" s="76"/>
-      <c r="CP11" s="86"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="19"/>
+      <c r="AF11" s="19"/>
+      <c r="AG11" s="19"/>
+      <c r="AH11" s="19"/>
+      <c r="AI11" s="19"/>
+      <c r="AJ11" s="19"/>
+      <c r="AK11" s="78"/>
+      <c r="AL11" s="78"/>
+      <c r="AM11" s="19"/>
+      <c r="AN11" s="19"/>
+      <c r="AO11" s="19"/>
+      <c r="AP11" s="19"/>
+      <c r="AQ11" s="19"/>
+      <c r="AR11" s="19"/>
+      <c r="AS11" s="19"/>
+      <c r="AT11" s="19"/>
+      <c r="AU11" s="19"/>
+      <c r="AV11" s="19"/>
+      <c r="AW11" s="19"/>
+      <c r="AX11" s="19"/>
+      <c r="AY11" s="19"/>
+      <c r="AZ11" s="19"/>
+      <c r="BA11" s="19"/>
+      <c r="BB11" s="19"/>
+      <c r="BC11" s="19"/>
+      <c r="BD11" s="19"/>
+      <c r="BE11" s="19"/>
+      <c r="BF11" s="19"/>
+      <c r="BG11" s="19"/>
+      <c r="BH11" s="42"/>
+      <c r="BI11" s="19"/>
+      <c r="BJ11" s="19"/>
+      <c r="BK11" s="19"/>
+      <c r="BL11" s="19"/>
+      <c r="BM11" s="19"/>
+      <c r="BN11" s="19"/>
+      <c r="BO11" s="19"/>
+      <c r="BP11" s="78"/>
+      <c r="BQ11" s="42"/>
+      <c r="BR11" s="42"/>
+      <c r="BS11" s="42"/>
+      <c r="BT11" s="42"/>
+      <c r="BU11" s="42"/>
+      <c r="BV11" s="42"/>
+      <c r="BW11" s="42"/>
+      <c r="BX11" s="42"/>
+      <c r="BY11" s="42"/>
+      <c r="BZ11" s="42"/>
+      <c r="CA11" s="42"/>
+      <c r="CB11" s="42"/>
+      <c r="CC11" s="42"/>
+      <c r="CD11" s="42"/>
+      <c r="CE11" s="42"/>
+      <c r="CF11" s="42"/>
+      <c r="CG11" s="74"/>
+      <c r="CH11" s="42"/>
+      <c r="CI11" s="74"/>
+      <c r="CJ11" s="74"/>
+      <c r="CK11" s="74"/>
+      <c r="CL11" s="74"/>
+      <c r="CM11" s="74"/>
+      <c r="CN11" s="74"/>
+      <c r="CO11" s="74"/>
+      <c r="CP11" s="84"/>
       <c r="CQ11"/>
       <c r="CR11"/>
       <c r="CS11"/>
@@ -3677,109 +3671,109 @@
       <c r="DQ11"/>
     </row>
     <row r="12" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23"/>
-      <c r="B12" s="98" t="s">
+      <c r="A12" s="22"/>
+      <c r="B12" s="100" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="98"/>
+      <c r="C12" s="100"/>
       <c r="D12" s="13">
         <v>1</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="40">
         <v>45909</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="40">
         <f>E12+3</f>
         <v>45912</v>
       </c>
-      <c r="G12" s="48"/>
+      <c r="G12" s="47"/>
       <c r="H12" s="12"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="20"/>
-      <c r="T12" s="20"/>
-      <c r="U12" s="20"/>
-      <c r="V12" s="20"/>
-      <c r="W12" s="20"/>
-      <c r="X12" s="20"/>
-      <c r="Y12" s="20"/>
-      <c r="Z12" s="20"/>
-      <c r="AA12" s="20"/>
-      <c r="AB12" s="20"/>
-      <c r="AC12" s="20"/>
-      <c r="AD12" s="20"/>
-      <c r="AE12" s="20"/>
-      <c r="AF12" s="20"/>
-      <c r="AG12" s="20"/>
-      <c r="AH12" s="20"/>
-      <c r="AI12" s="20"/>
-      <c r="AJ12" s="20"/>
-      <c r="AK12" s="80"/>
-      <c r="AL12" s="80"/>
-      <c r="AM12" s="20"/>
-      <c r="AN12" s="20"/>
-      <c r="AO12" s="20"/>
-      <c r="AP12" s="20"/>
-      <c r="AQ12" s="20"/>
-      <c r="AR12" s="20"/>
-      <c r="AS12" s="20"/>
-      <c r="AT12" s="20"/>
-      <c r="AU12" s="20"/>
-      <c r="AV12" s="20"/>
-      <c r="AW12" s="20"/>
-      <c r="AX12" s="20"/>
-      <c r="AY12" s="20"/>
-      <c r="AZ12" s="20"/>
-      <c r="BA12" s="20"/>
-      <c r="BB12" s="20"/>
-      <c r="BC12" s="20"/>
-      <c r="BD12" s="20"/>
-      <c r="BE12" s="20"/>
-      <c r="BF12" s="20"/>
-      <c r="BG12" s="20"/>
-      <c r="BH12" s="43"/>
-      <c r="BI12" s="20"/>
-      <c r="BJ12" s="20"/>
-      <c r="BK12" s="20"/>
-      <c r="BL12" s="20"/>
-      <c r="BM12" s="20"/>
-      <c r="BN12" s="20"/>
-      <c r="BO12" s="20"/>
-      <c r="BP12" s="80"/>
-      <c r="BQ12" s="43"/>
-      <c r="BR12" s="43"/>
-      <c r="BS12" s="43"/>
-      <c r="BT12" s="43"/>
-      <c r="BU12" s="43"/>
-      <c r="BV12" s="43"/>
-      <c r="BW12" s="43"/>
-      <c r="BX12" s="43"/>
-      <c r="BY12" s="43"/>
-      <c r="BZ12" s="43"/>
-      <c r="CA12" s="43"/>
-      <c r="CB12" s="43"/>
-      <c r="CC12" s="43"/>
-      <c r="CD12" s="43"/>
-      <c r="CE12" s="43"/>
-      <c r="CF12" s="43"/>
-      <c r="CG12" s="76"/>
-      <c r="CH12" s="43"/>
-      <c r="CI12" s="76"/>
-      <c r="CJ12" s="76"/>
-      <c r="CK12" s="76"/>
-      <c r="CL12" s="76"/>
-      <c r="CM12" s="76"/>
-      <c r="CN12" s="76"/>
-      <c r="CO12" s="76"/>
-      <c r="CP12" s="86"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="19"/>
+      <c r="AC12" s="19"/>
+      <c r="AD12" s="19"/>
+      <c r="AE12" s="19"/>
+      <c r="AF12" s="19"/>
+      <c r="AG12" s="19"/>
+      <c r="AH12" s="19"/>
+      <c r="AI12" s="19"/>
+      <c r="AJ12" s="19"/>
+      <c r="AK12" s="78"/>
+      <c r="AL12" s="78"/>
+      <c r="AM12" s="19"/>
+      <c r="AN12" s="19"/>
+      <c r="AO12" s="19"/>
+      <c r="AP12" s="19"/>
+      <c r="AQ12" s="19"/>
+      <c r="AR12" s="19"/>
+      <c r="AS12" s="19"/>
+      <c r="AT12" s="19"/>
+      <c r="AU12" s="19"/>
+      <c r="AV12" s="19"/>
+      <c r="AW12" s="19"/>
+      <c r="AX12" s="19"/>
+      <c r="AY12" s="19"/>
+      <c r="AZ12" s="19"/>
+      <c r="BA12" s="19"/>
+      <c r="BB12" s="19"/>
+      <c r="BC12" s="19"/>
+      <c r="BD12" s="19"/>
+      <c r="BE12" s="19"/>
+      <c r="BF12" s="19"/>
+      <c r="BG12" s="19"/>
+      <c r="BH12" s="42"/>
+      <c r="BI12" s="19"/>
+      <c r="BJ12" s="19"/>
+      <c r="BK12" s="19"/>
+      <c r="BL12" s="19"/>
+      <c r="BM12" s="19"/>
+      <c r="BN12" s="19"/>
+      <c r="BO12" s="19"/>
+      <c r="BP12" s="78"/>
+      <c r="BQ12" s="42"/>
+      <c r="BR12" s="42"/>
+      <c r="BS12" s="42"/>
+      <c r="BT12" s="42"/>
+      <c r="BU12" s="42"/>
+      <c r="BV12" s="42"/>
+      <c r="BW12" s="42"/>
+      <c r="BX12" s="42"/>
+      <c r="BY12" s="42"/>
+      <c r="BZ12" s="42"/>
+      <c r="CA12" s="42"/>
+      <c r="CB12" s="42"/>
+      <c r="CC12" s="42"/>
+      <c r="CD12" s="42"/>
+      <c r="CE12" s="42"/>
+      <c r="CF12" s="42"/>
+      <c r="CG12" s="74"/>
+      <c r="CH12" s="42"/>
+      <c r="CI12" s="74"/>
+      <c r="CJ12" s="74"/>
+      <c r="CK12" s="74"/>
+      <c r="CL12" s="74"/>
+      <c r="CM12" s="74"/>
+      <c r="CN12" s="74"/>
+      <c r="CO12" s="74"/>
+      <c r="CP12" s="84"/>
       <c r="CQ12"/>
       <c r="CR12"/>
       <c r="CS12"/>
@@ -3809,108 +3803,108 @@
       <c r="DQ12"/>
     </row>
     <row r="13" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="23"/>
-      <c r="B13" s="98" t="s">
+      <c r="A13" s="22"/>
+      <c r="B13" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="98"/>
+      <c r="C13" s="100"/>
       <c r="D13" s="13">
         <v>1</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="40">
         <v>45912</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="40">
         <v>45917</v>
       </c>
-      <c r="G13" s="48"/>
+      <c r="G13" s="47"/>
       <c r="H13" s="12"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="20"/>
-      <c r="V13" s="20"/>
-      <c r="W13" s="20"/>
-      <c r="X13" s="20"/>
-      <c r="Y13" s="20"/>
-      <c r="Z13" s="20"/>
-      <c r="AA13" s="20"/>
-      <c r="AB13" s="20"/>
-      <c r="AC13" s="20"/>
-      <c r="AD13" s="20"/>
-      <c r="AE13" s="20"/>
-      <c r="AF13" s="20"/>
-      <c r="AG13" s="20"/>
-      <c r="AH13" s="20"/>
-      <c r="AI13" s="20"/>
-      <c r="AJ13" s="20"/>
-      <c r="AK13" s="80"/>
-      <c r="AL13" s="80"/>
-      <c r="AM13" s="20"/>
-      <c r="AN13" s="20"/>
-      <c r="AO13" s="20"/>
-      <c r="AP13" s="20"/>
-      <c r="AQ13" s="20"/>
-      <c r="AR13" s="20"/>
-      <c r="AS13" s="20"/>
-      <c r="AT13" s="20"/>
-      <c r="AU13" s="20"/>
-      <c r="AV13" s="20"/>
-      <c r="AW13" s="20"/>
-      <c r="AX13" s="20"/>
-      <c r="AY13" s="20"/>
-      <c r="AZ13" s="20"/>
-      <c r="BA13" s="20"/>
-      <c r="BB13" s="20"/>
-      <c r="BC13" s="20"/>
-      <c r="BD13" s="20"/>
-      <c r="BE13" s="20"/>
-      <c r="BF13" s="20"/>
-      <c r="BG13" s="20"/>
-      <c r="BH13" s="20"/>
-      <c r="BI13" s="20"/>
-      <c r="BJ13" s="20"/>
-      <c r="BK13" s="20"/>
-      <c r="BL13" s="20"/>
-      <c r="BM13" s="20"/>
-      <c r="BN13" s="20"/>
-      <c r="BO13" s="20"/>
-      <c r="BP13" s="80"/>
-      <c r="BQ13" s="20"/>
-      <c r="BR13" s="20"/>
-      <c r="BS13" s="20"/>
-      <c r="BT13" s="20"/>
-      <c r="BU13" s="20"/>
-      <c r="BV13" s="20"/>
-      <c r="BW13" s="20"/>
-      <c r="BX13" s="20"/>
-      <c r="BY13" s="20"/>
-      <c r="BZ13" s="20"/>
-      <c r="CA13" s="20"/>
-      <c r="CB13" s="20"/>
-      <c r="CC13" s="20"/>
-      <c r="CD13" s="20"/>
-      <c r="CE13" s="20"/>
-      <c r="CF13" s="20"/>
-      <c r="CG13" s="73"/>
-      <c r="CH13" s="20"/>
-      <c r="CI13" s="20"/>
-      <c r="CJ13" s="20"/>
-      <c r="CK13" s="20"/>
-      <c r="CL13" s="20"/>
-      <c r="CM13" s="20"/>
-      <c r="CN13" s="20"/>
-      <c r="CO13" s="73"/>
-      <c r="CP13" s="86"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="19"/>
+      <c r="AA13" s="19"/>
+      <c r="AB13" s="19"/>
+      <c r="AC13" s="19"/>
+      <c r="AD13" s="19"/>
+      <c r="AE13" s="19"/>
+      <c r="AF13" s="19"/>
+      <c r="AG13" s="19"/>
+      <c r="AH13" s="19"/>
+      <c r="AI13" s="19"/>
+      <c r="AJ13" s="19"/>
+      <c r="AK13" s="78"/>
+      <c r="AL13" s="78"/>
+      <c r="AM13" s="19"/>
+      <c r="AN13" s="19"/>
+      <c r="AO13" s="19"/>
+      <c r="AP13" s="19"/>
+      <c r="AQ13" s="19"/>
+      <c r="AR13" s="19"/>
+      <c r="AS13" s="19"/>
+      <c r="AT13" s="19"/>
+      <c r="AU13" s="19"/>
+      <c r="AV13" s="19"/>
+      <c r="AW13" s="19"/>
+      <c r="AX13" s="19"/>
+      <c r="AY13" s="19"/>
+      <c r="AZ13" s="19"/>
+      <c r="BA13" s="19"/>
+      <c r="BB13" s="19"/>
+      <c r="BC13" s="19"/>
+      <c r="BD13" s="19"/>
+      <c r="BE13" s="19"/>
+      <c r="BF13" s="19"/>
+      <c r="BG13" s="19"/>
+      <c r="BH13" s="19"/>
+      <c r="BI13" s="19"/>
+      <c r="BJ13" s="19"/>
+      <c r="BK13" s="19"/>
+      <c r="BL13" s="19"/>
+      <c r="BM13" s="19"/>
+      <c r="BN13" s="19"/>
+      <c r="BO13" s="19"/>
+      <c r="BP13" s="78"/>
+      <c r="BQ13" s="19"/>
+      <c r="BR13" s="19"/>
+      <c r="BS13" s="19"/>
+      <c r="BT13" s="19"/>
+      <c r="BU13" s="19"/>
+      <c r="BV13" s="19"/>
+      <c r="BW13" s="19"/>
+      <c r="BX13" s="19"/>
+      <c r="BY13" s="19"/>
+      <c r="BZ13" s="19"/>
+      <c r="CA13" s="19"/>
+      <c r="CB13" s="19"/>
+      <c r="CC13" s="19"/>
+      <c r="CD13" s="19"/>
+      <c r="CE13" s="19"/>
+      <c r="CF13" s="19"/>
+      <c r="CG13" s="71"/>
+      <c r="CH13" s="19"/>
+      <c r="CI13" s="19"/>
+      <c r="CJ13" s="19"/>
+      <c r="CK13" s="19"/>
+      <c r="CL13" s="19"/>
+      <c r="CM13" s="19"/>
+      <c r="CN13" s="19"/>
+      <c r="CO13" s="71"/>
+      <c r="CP13" s="84"/>
       <c r="CQ13"/>
       <c r="CR13"/>
       <c r="CS13"/>
@@ -3940,107 +3934,107 @@
       <c r="DQ13"/>
     </row>
     <row r="14" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="23" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="29"/>
+      <c r="C14" s="28"/>
       <c r="D14" s="15"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="49"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="48"/>
       <c r="H14" s="12" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I14" s="90"/>
-      <c r="J14" s="91"/>
-      <c r="K14" s="91"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="91"/>
-      <c r="N14" s="91"/>
-      <c r="O14" s="91"/>
-      <c r="P14" s="91"/>
-      <c r="Q14" s="91"/>
-      <c r="R14" s="91"/>
-      <c r="S14" s="91"/>
-      <c r="T14" s="91"/>
-      <c r="U14" s="91"/>
-      <c r="V14" s="91"/>
-      <c r="W14" s="91"/>
-      <c r="X14" s="91"/>
-      <c r="Y14" s="91"/>
-      <c r="Z14" s="91"/>
-      <c r="AA14" s="91"/>
-      <c r="AB14" s="91"/>
-      <c r="AC14" s="91"/>
-      <c r="AD14" s="91"/>
-      <c r="AE14" s="91"/>
-      <c r="AF14" s="91"/>
-      <c r="AG14" s="91"/>
-      <c r="AH14" s="91"/>
-      <c r="AI14" s="91"/>
-      <c r="AJ14" s="91"/>
-      <c r="AK14" s="91"/>
-      <c r="AL14" s="91"/>
-      <c r="AM14" s="91"/>
-      <c r="AN14" s="91"/>
-      <c r="AO14" s="91"/>
-      <c r="AP14" s="91"/>
-      <c r="AQ14" s="91"/>
-      <c r="AR14" s="91"/>
-      <c r="AS14" s="91"/>
-      <c r="AT14" s="91"/>
-      <c r="AU14" s="91"/>
-      <c r="AV14" s="91"/>
-      <c r="AW14" s="91"/>
-      <c r="AX14" s="91"/>
-      <c r="AY14" s="91"/>
-      <c r="AZ14" s="91"/>
-      <c r="BA14" s="91"/>
-      <c r="BB14" s="91"/>
-      <c r="BC14" s="91"/>
-      <c r="BD14" s="91"/>
-      <c r="BE14" s="91"/>
-      <c r="BF14" s="91"/>
-      <c r="BG14" s="91"/>
-      <c r="BH14" s="91"/>
-      <c r="BI14" s="91"/>
-      <c r="BJ14" s="91"/>
-      <c r="BK14" s="91"/>
-      <c r="BL14" s="91"/>
-      <c r="BM14" s="91"/>
-      <c r="BN14" s="91"/>
-      <c r="BO14" s="91"/>
-      <c r="BP14" s="91"/>
-      <c r="BQ14" s="91"/>
-      <c r="BR14" s="91"/>
-      <c r="BS14" s="91"/>
-      <c r="BT14" s="91"/>
-      <c r="BU14" s="91"/>
-      <c r="BV14" s="91"/>
-      <c r="BW14" s="91"/>
-      <c r="BX14" s="91"/>
-      <c r="BY14" s="91"/>
-      <c r="BZ14" s="91"/>
-      <c r="CA14" s="91"/>
-      <c r="CB14" s="91"/>
-      <c r="CC14" s="91"/>
-      <c r="CD14" s="91"/>
-      <c r="CE14" s="91"/>
-      <c r="CF14" s="91"/>
-      <c r="CG14" s="91"/>
-      <c r="CH14" s="91"/>
-      <c r="CI14" s="91"/>
-      <c r="CJ14" s="91"/>
-      <c r="CK14" s="91"/>
-      <c r="CL14" s="91"/>
-      <c r="CM14" s="91"/>
-      <c r="CN14" s="91"/>
-      <c r="CO14" s="92"/>
-      <c r="CP14" s="86"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="93"/>
+      <c r="K14" s="93"/>
+      <c r="L14" s="93"/>
+      <c r="M14" s="93"/>
+      <c r="N14" s="93"/>
+      <c r="O14" s="93"/>
+      <c r="P14" s="93"/>
+      <c r="Q14" s="93"/>
+      <c r="R14" s="93"/>
+      <c r="S14" s="93"/>
+      <c r="T14" s="93"/>
+      <c r="U14" s="93"/>
+      <c r="V14" s="93"/>
+      <c r="W14" s="93"/>
+      <c r="X14" s="93"/>
+      <c r="Y14" s="93"/>
+      <c r="Z14" s="93"/>
+      <c r="AA14" s="93"/>
+      <c r="AB14" s="93"/>
+      <c r="AC14" s="93"/>
+      <c r="AD14" s="93"/>
+      <c r="AE14" s="93"/>
+      <c r="AF14" s="93"/>
+      <c r="AG14" s="93"/>
+      <c r="AH14" s="93"/>
+      <c r="AI14" s="93"/>
+      <c r="AJ14" s="93"/>
+      <c r="AK14" s="93"/>
+      <c r="AL14" s="93"/>
+      <c r="AM14" s="93"/>
+      <c r="AN14" s="93"/>
+      <c r="AO14" s="93"/>
+      <c r="AP14" s="93"/>
+      <c r="AQ14" s="93"/>
+      <c r="AR14" s="93"/>
+      <c r="AS14" s="93"/>
+      <c r="AT14" s="93"/>
+      <c r="AU14" s="93"/>
+      <c r="AV14" s="93"/>
+      <c r="AW14" s="93"/>
+      <c r="AX14" s="93"/>
+      <c r="AY14" s="93"/>
+      <c r="AZ14" s="93"/>
+      <c r="BA14" s="93"/>
+      <c r="BB14" s="93"/>
+      <c r="BC14" s="93"/>
+      <c r="BD14" s="93"/>
+      <c r="BE14" s="93"/>
+      <c r="BF14" s="93"/>
+      <c r="BG14" s="93"/>
+      <c r="BH14" s="93"/>
+      <c r="BI14" s="93"/>
+      <c r="BJ14" s="93"/>
+      <c r="BK14" s="93"/>
+      <c r="BL14" s="93"/>
+      <c r="BM14" s="93"/>
+      <c r="BN14" s="93"/>
+      <c r="BO14" s="93"/>
+      <c r="BP14" s="93"/>
+      <c r="BQ14" s="93"/>
+      <c r="BR14" s="93"/>
+      <c r="BS14" s="93"/>
+      <c r="BT14" s="93"/>
+      <c r="BU14" s="93"/>
+      <c r="BV14" s="93"/>
+      <c r="BW14" s="93"/>
+      <c r="BX14" s="93"/>
+      <c r="BY14" s="93"/>
+      <c r="BZ14" s="93"/>
+      <c r="CA14" s="93"/>
+      <c r="CB14" s="93"/>
+      <c r="CC14" s="93"/>
+      <c r="CD14" s="93"/>
+      <c r="CE14" s="93"/>
+      <c r="CF14" s="93"/>
+      <c r="CG14" s="93"/>
+      <c r="CH14" s="93"/>
+      <c r="CI14" s="93"/>
+      <c r="CJ14" s="93"/>
+      <c r="CK14" s="93"/>
+      <c r="CL14" s="93"/>
+      <c r="CM14" s="93"/>
+      <c r="CN14" s="93"/>
+      <c r="CO14" s="94"/>
+      <c r="CP14" s="84"/>
       <c r="CQ14"/>
       <c r="CR14"/>
       <c r="CS14"/>
@@ -4070,108 +4064,108 @@
       <c r="DQ14"/>
     </row>
     <row r="15" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24"/>
-      <c r="B15" s="33" t="s">
+      <c r="A15" s="23"/>
+      <c r="B15" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="30"/>
+      <c r="C15" s="29"/>
       <c r="D15" s="13">
         <v>1</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="41">
         <v>45917</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="41">
         <v>45917</v>
       </c>
-      <c r="G15" s="50"/>
+      <c r="G15" s="49"/>
       <c r="H15" s="12"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20"/>
-      <c r="T15" s="20"/>
-      <c r="U15" s="20"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="20"/>
-      <c r="X15" s="20"/>
-      <c r="Y15" s="20"/>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="20"/>
-      <c r="AB15" s="20"/>
-      <c r="AC15" s="20"/>
-      <c r="AD15" s="20"/>
-      <c r="AE15" s="20"/>
-      <c r="AF15" s="20"/>
-      <c r="AG15" s="20"/>
-      <c r="AH15" s="20"/>
-      <c r="AI15" s="20"/>
-      <c r="AJ15" s="20"/>
-      <c r="AK15" s="80"/>
-      <c r="AL15" s="80"/>
-      <c r="AM15" s="20"/>
-      <c r="AN15" s="20"/>
-      <c r="AO15" s="20"/>
-      <c r="AP15" s="20"/>
-      <c r="AQ15" s="20"/>
-      <c r="AR15" s="20"/>
-      <c r="AS15" s="20"/>
-      <c r="AT15" s="20"/>
-      <c r="AU15" s="20"/>
-      <c r="AV15" s="20"/>
-      <c r="AW15" s="20"/>
-      <c r="AX15" s="20"/>
-      <c r="AY15" s="20"/>
-      <c r="AZ15" s="20"/>
-      <c r="BA15" s="20"/>
-      <c r="BB15" s="20"/>
-      <c r="BC15" s="20"/>
-      <c r="BD15" s="20"/>
-      <c r="BE15" s="20"/>
-      <c r="BF15" s="20"/>
-      <c r="BG15" s="20"/>
-      <c r="BH15" s="43"/>
-      <c r="BI15" s="20"/>
-      <c r="BJ15" s="20"/>
-      <c r="BK15" s="20"/>
-      <c r="BL15" s="20"/>
-      <c r="BM15" s="20"/>
-      <c r="BN15" s="20"/>
-      <c r="BO15" s="20"/>
-      <c r="BP15" s="80"/>
-      <c r="BQ15" s="43"/>
-      <c r="BR15" s="43"/>
-      <c r="BS15" s="43"/>
-      <c r="BT15" s="43"/>
-      <c r="BU15" s="43"/>
-      <c r="BV15" s="43"/>
-      <c r="BW15" s="43"/>
-      <c r="BX15" s="43"/>
-      <c r="BY15" s="43"/>
-      <c r="BZ15" s="43"/>
-      <c r="CA15" s="43"/>
-      <c r="CB15" s="43"/>
-      <c r="CC15" s="43"/>
-      <c r="CD15" s="43"/>
-      <c r="CE15" s="43"/>
-      <c r="CF15" s="43"/>
-      <c r="CG15" s="76"/>
-      <c r="CH15" s="20"/>
-      <c r="CI15" s="20"/>
-      <c r="CJ15" s="20"/>
-      <c r="CK15" s="20"/>
-      <c r="CL15" s="20"/>
-      <c r="CM15" s="20"/>
-      <c r="CN15" s="20"/>
-      <c r="CO15" s="73"/>
-      <c r="CP15" s="86"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="19"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="19"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="19"/>
+      <c r="AA15" s="19"/>
+      <c r="AB15" s="19"/>
+      <c r="AC15" s="19"/>
+      <c r="AD15" s="19"/>
+      <c r="AE15" s="19"/>
+      <c r="AF15" s="19"/>
+      <c r="AG15" s="19"/>
+      <c r="AH15" s="19"/>
+      <c r="AI15" s="19"/>
+      <c r="AJ15" s="19"/>
+      <c r="AK15" s="78"/>
+      <c r="AL15" s="78"/>
+      <c r="AM15" s="19"/>
+      <c r="AN15" s="19"/>
+      <c r="AO15" s="19"/>
+      <c r="AP15" s="19"/>
+      <c r="AQ15" s="19"/>
+      <c r="AR15" s="19"/>
+      <c r="AS15" s="19"/>
+      <c r="AT15" s="19"/>
+      <c r="AU15" s="19"/>
+      <c r="AV15" s="19"/>
+      <c r="AW15" s="19"/>
+      <c r="AX15" s="19"/>
+      <c r="AY15" s="19"/>
+      <c r="AZ15" s="19"/>
+      <c r="BA15" s="19"/>
+      <c r="BB15" s="19"/>
+      <c r="BC15" s="19"/>
+      <c r="BD15" s="19"/>
+      <c r="BE15" s="19"/>
+      <c r="BF15" s="19"/>
+      <c r="BG15" s="19"/>
+      <c r="BH15" s="42"/>
+      <c r="BI15" s="19"/>
+      <c r="BJ15" s="19"/>
+      <c r="BK15" s="19"/>
+      <c r="BL15" s="19"/>
+      <c r="BM15" s="19"/>
+      <c r="BN15" s="19"/>
+      <c r="BO15" s="19"/>
+      <c r="BP15" s="78"/>
+      <c r="BQ15" s="42"/>
+      <c r="BR15" s="42"/>
+      <c r="BS15" s="42"/>
+      <c r="BT15" s="42"/>
+      <c r="BU15" s="42"/>
+      <c r="BV15" s="42"/>
+      <c r="BW15" s="42"/>
+      <c r="BX15" s="42"/>
+      <c r="BY15" s="42"/>
+      <c r="BZ15" s="42"/>
+      <c r="CA15" s="42"/>
+      <c r="CB15" s="42"/>
+      <c r="CC15" s="42"/>
+      <c r="CD15" s="42"/>
+      <c r="CE15" s="42"/>
+      <c r="CF15" s="42"/>
+      <c r="CG15" s="74"/>
+      <c r="CH15" s="19"/>
+      <c r="CI15" s="19"/>
+      <c r="CJ15" s="19"/>
+      <c r="CK15" s="19"/>
+      <c r="CL15" s="19"/>
+      <c r="CM15" s="19"/>
+      <c r="CN15" s="19"/>
+      <c r="CO15" s="71"/>
+      <c r="CP15" s="84"/>
       <c r="CQ15"/>
       <c r="CR15"/>
       <c r="CS15"/>
@@ -4201,108 +4195,108 @@
       <c r="DQ15"/>
     </row>
     <row r="16" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24"/>
-      <c r="B16" s="33" t="s">
+      <c r="A16" s="23"/>
+      <c r="B16" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="30"/>
+      <c r="C16" s="29"/>
       <c r="D16" s="16">
         <v>1</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="41">
         <v>45922</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="41">
         <v>45954</v>
       </c>
-      <c r="G16" s="50"/>
+      <c r="G16" s="49"/>
       <c r="H16" s="12"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
-      <c r="U16" s="20"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="20"/>
-      <c r="X16" s="20"/>
-      <c r="Y16" s="20"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16" s="20"/>
-      <c r="AB16" s="20"/>
-      <c r="AC16" s="20"/>
-      <c r="AD16" s="20"/>
-      <c r="AE16" s="20"/>
-      <c r="AF16" s="20"/>
-      <c r="AG16" s="20"/>
-      <c r="AH16" s="20"/>
-      <c r="AI16" s="20"/>
-      <c r="AJ16" s="20"/>
-      <c r="AK16" s="80"/>
-      <c r="AL16" s="80"/>
-      <c r="AM16" s="20"/>
-      <c r="AN16" s="20"/>
-      <c r="AO16" s="20"/>
-      <c r="AP16" s="20"/>
-      <c r="AQ16" s="20"/>
-      <c r="AR16" s="20"/>
-      <c r="AS16" s="20"/>
-      <c r="AT16" s="20"/>
-      <c r="AU16" s="20"/>
-      <c r="AV16" s="20"/>
-      <c r="AW16" s="20"/>
-      <c r="AX16" s="20"/>
-      <c r="AY16" s="20"/>
-      <c r="AZ16" s="20"/>
-      <c r="BA16" s="20"/>
-      <c r="BB16" s="20"/>
-      <c r="BC16" s="20"/>
-      <c r="BD16" s="20"/>
-      <c r="BE16" s="20"/>
-      <c r="BF16" s="20"/>
-      <c r="BG16" s="20"/>
-      <c r="BH16" s="43"/>
-      <c r="BI16" s="20"/>
-      <c r="BJ16" s="20"/>
-      <c r="BK16" s="20"/>
-      <c r="BL16" s="20"/>
-      <c r="BM16" s="20"/>
-      <c r="BN16" s="20"/>
-      <c r="BO16" s="20"/>
-      <c r="BP16" s="80"/>
-      <c r="BQ16" s="43"/>
-      <c r="BR16" s="43"/>
-      <c r="BS16" s="43"/>
-      <c r="BT16" s="43"/>
-      <c r="BU16" s="43"/>
-      <c r="BV16" s="43"/>
-      <c r="BW16" s="43"/>
-      <c r="BX16" s="43"/>
-      <c r="BY16" s="43"/>
-      <c r="BZ16" s="43"/>
-      <c r="CA16" s="43"/>
-      <c r="CB16" s="43"/>
-      <c r="CC16" s="43"/>
-      <c r="CD16" s="43"/>
-      <c r="CE16" s="43"/>
-      <c r="CF16" s="43"/>
-      <c r="CG16" s="76"/>
-      <c r="CH16" s="20"/>
-      <c r="CI16" s="20"/>
-      <c r="CJ16" s="20"/>
-      <c r="CK16" s="20"/>
-      <c r="CL16" s="20"/>
-      <c r="CM16" s="20"/>
-      <c r="CN16" s="20"/>
-      <c r="CO16" s="73"/>
-      <c r="CP16" s="86"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="19"/>
+      <c r="X16" s="19"/>
+      <c r="Y16" s="19"/>
+      <c r="Z16" s="19"/>
+      <c r="AA16" s="19"/>
+      <c r="AB16" s="19"/>
+      <c r="AC16" s="19"/>
+      <c r="AD16" s="19"/>
+      <c r="AE16" s="19"/>
+      <c r="AF16" s="19"/>
+      <c r="AG16" s="19"/>
+      <c r="AH16" s="19"/>
+      <c r="AI16" s="19"/>
+      <c r="AJ16" s="19"/>
+      <c r="AK16" s="78"/>
+      <c r="AL16" s="78"/>
+      <c r="AM16" s="19"/>
+      <c r="AN16" s="19"/>
+      <c r="AO16" s="19"/>
+      <c r="AP16" s="19"/>
+      <c r="AQ16" s="19"/>
+      <c r="AR16" s="19"/>
+      <c r="AS16" s="19"/>
+      <c r="AT16" s="19"/>
+      <c r="AU16" s="19"/>
+      <c r="AV16" s="19"/>
+      <c r="AW16" s="19"/>
+      <c r="AX16" s="19"/>
+      <c r="AY16" s="19"/>
+      <c r="AZ16" s="19"/>
+      <c r="BA16" s="19"/>
+      <c r="BB16" s="19"/>
+      <c r="BC16" s="19"/>
+      <c r="BD16" s="19"/>
+      <c r="BE16" s="19"/>
+      <c r="BF16" s="19"/>
+      <c r="BG16" s="19"/>
+      <c r="BH16" s="42"/>
+      <c r="BI16" s="19"/>
+      <c r="BJ16" s="19"/>
+      <c r="BK16" s="19"/>
+      <c r="BL16" s="19"/>
+      <c r="BM16" s="19"/>
+      <c r="BN16" s="19"/>
+      <c r="BO16" s="19"/>
+      <c r="BP16" s="78"/>
+      <c r="BQ16" s="42"/>
+      <c r="BR16" s="42"/>
+      <c r="BS16" s="42"/>
+      <c r="BT16" s="42"/>
+      <c r="BU16" s="42"/>
+      <c r="BV16" s="42"/>
+      <c r="BW16" s="42"/>
+      <c r="BX16" s="42"/>
+      <c r="BY16" s="42"/>
+      <c r="BZ16" s="42"/>
+      <c r="CA16" s="42"/>
+      <c r="CB16" s="42"/>
+      <c r="CC16" s="42"/>
+      <c r="CD16" s="42"/>
+      <c r="CE16" s="42"/>
+      <c r="CF16" s="42"/>
+      <c r="CG16" s="74"/>
+      <c r="CH16" s="19"/>
+      <c r="CI16" s="19"/>
+      <c r="CJ16" s="19"/>
+      <c r="CK16" s="19"/>
+      <c r="CL16" s="19"/>
+      <c r="CM16" s="19"/>
+      <c r="CN16" s="19"/>
+      <c r="CO16" s="71"/>
+      <c r="CP16" s="84"/>
       <c r="CQ16"/>
       <c r="CR16"/>
       <c r="CS16"/>
@@ -4332,108 +4326,108 @@
       <c r="DQ16"/>
     </row>
     <row r="17" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24"/>
-      <c r="B17" s="33" t="s">
+      <c r="A17" s="23"/>
+      <c r="B17" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="30"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="16">
         <v>1</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="41">
         <v>45926</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="41">
         <v>45960</v>
       </c>
-      <c r="G17" s="50"/>
+      <c r="G17" s="49"/>
       <c r="H17" s="12"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="20"/>
-      <c r="U17" s="20"/>
-      <c r="V17" s="20"/>
-      <c r="W17" s="20"/>
-      <c r="X17" s="20"/>
-      <c r="Y17" s="20"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="20"/>
-      <c r="AB17" s="20"/>
-      <c r="AC17" s="20"/>
-      <c r="AD17" s="20"/>
-      <c r="AE17" s="20"/>
-      <c r="AF17" s="20"/>
-      <c r="AG17" s="20"/>
-      <c r="AH17" s="20"/>
-      <c r="AI17" s="20"/>
-      <c r="AJ17" s="20"/>
-      <c r="AK17" s="80"/>
-      <c r="AL17" s="80"/>
-      <c r="AM17" s="20"/>
-      <c r="AN17" s="20"/>
-      <c r="AO17" s="20"/>
-      <c r="AP17" s="20"/>
-      <c r="AQ17" s="20"/>
-      <c r="AR17" s="20"/>
-      <c r="AS17" s="20"/>
-      <c r="AT17" s="20"/>
-      <c r="AU17" s="20"/>
-      <c r="AV17" s="20"/>
-      <c r="AW17" s="20"/>
-      <c r="AX17" s="20"/>
-      <c r="AY17" s="20"/>
-      <c r="AZ17" s="20"/>
-      <c r="BA17" s="20"/>
-      <c r="BB17" s="20"/>
-      <c r="BC17" s="20"/>
-      <c r="BD17" s="20"/>
-      <c r="BE17" s="20"/>
-      <c r="BF17" s="20"/>
-      <c r="BG17" s="20"/>
-      <c r="BH17" s="43"/>
-      <c r="BI17" s="20"/>
-      <c r="BJ17" s="20"/>
-      <c r="BK17" s="20"/>
-      <c r="BL17" s="20"/>
-      <c r="BM17" s="20"/>
-      <c r="BN17" s="20"/>
-      <c r="BO17" s="20"/>
-      <c r="BP17" s="80"/>
-      <c r="BQ17" s="43"/>
-      <c r="BR17" s="43"/>
-      <c r="BS17" s="43"/>
-      <c r="BT17" s="43"/>
-      <c r="BU17" s="43"/>
-      <c r="BV17" s="43"/>
-      <c r="BW17" s="43"/>
-      <c r="BX17" s="43"/>
-      <c r="BY17" s="43"/>
-      <c r="BZ17" s="43"/>
-      <c r="CA17" s="43"/>
-      <c r="CB17" s="43"/>
-      <c r="CC17" s="43"/>
-      <c r="CD17" s="43"/>
-      <c r="CE17" s="43"/>
-      <c r="CF17" s="43"/>
-      <c r="CG17" s="76"/>
-      <c r="CH17" s="20"/>
-      <c r="CI17" s="20"/>
-      <c r="CJ17" s="20"/>
-      <c r="CK17" s="20"/>
-      <c r="CL17" s="20"/>
-      <c r="CM17" s="20"/>
-      <c r="CN17" s="20"/>
-      <c r="CO17" s="73"/>
-      <c r="CP17" s="86"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="19"/>
+      <c r="V17" s="19"/>
+      <c r="W17" s="19"/>
+      <c r="X17" s="19"/>
+      <c r="Y17" s="19"/>
+      <c r="Z17" s="19"/>
+      <c r="AA17" s="19"/>
+      <c r="AB17" s="19"/>
+      <c r="AC17" s="19"/>
+      <c r="AD17" s="19"/>
+      <c r="AE17" s="19"/>
+      <c r="AF17" s="19"/>
+      <c r="AG17" s="19"/>
+      <c r="AH17" s="19"/>
+      <c r="AI17" s="19"/>
+      <c r="AJ17" s="19"/>
+      <c r="AK17" s="78"/>
+      <c r="AL17" s="78"/>
+      <c r="AM17" s="19"/>
+      <c r="AN17" s="19"/>
+      <c r="AO17" s="19"/>
+      <c r="AP17" s="19"/>
+      <c r="AQ17" s="19"/>
+      <c r="AR17" s="19"/>
+      <c r="AS17" s="19"/>
+      <c r="AT17" s="19"/>
+      <c r="AU17" s="19"/>
+      <c r="AV17" s="19"/>
+      <c r="AW17" s="19"/>
+      <c r="AX17" s="19"/>
+      <c r="AY17" s="19"/>
+      <c r="AZ17" s="19"/>
+      <c r="BA17" s="19"/>
+      <c r="BB17" s="19"/>
+      <c r="BC17" s="19"/>
+      <c r="BD17" s="19"/>
+      <c r="BE17" s="19"/>
+      <c r="BF17" s="19"/>
+      <c r="BG17" s="19"/>
+      <c r="BH17" s="42"/>
+      <c r="BI17" s="19"/>
+      <c r="BJ17" s="19"/>
+      <c r="BK17" s="19"/>
+      <c r="BL17" s="19"/>
+      <c r="BM17" s="19"/>
+      <c r="BN17" s="19"/>
+      <c r="BO17" s="19"/>
+      <c r="BP17" s="78"/>
+      <c r="BQ17" s="42"/>
+      <c r="BR17" s="42"/>
+      <c r="BS17" s="42"/>
+      <c r="BT17" s="42"/>
+      <c r="BU17" s="42"/>
+      <c r="BV17" s="42"/>
+      <c r="BW17" s="42"/>
+      <c r="BX17" s="42"/>
+      <c r="BY17" s="42"/>
+      <c r="BZ17" s="42"/>
+      <c r="CA17" s="42"/>
+      <c r="CB17" s="42"/>
+      <c r="CC17" s="42"/>
+      <c r="CD17" s="42"/>
+      <c r="CE17" s="42"/>
+      <c r="CF17" s="42"/>
+      <c r="CG17" s="74"/>
+      <c r="CH17" s="19"/>
+      <c r="CI17" s="19"/>
+      <c r="CJ17" s="19"/>
+      <c r="CK17" s="19"/>
+      <c r="CL17" s="19"/>
+      <c r="CM17" s="19"/>
+      <c r="CN17" s="19"/>
+      <c r="CO17" s="71"/>
+      <c r="CP17" s="84"/>
       <c r="CQ17"/>
       <c r="CR17"/>
       <c r="CS17"/>
@@ -4463,108 +4457,108 @@
       <c r="DQ17"/>
     </row>
     <row r="18" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24"/>
-      <c r="B18" s="33" t="s">
+      <c r="A18" s="23"/>
+      <c r="B18" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="30"/>
+      <c r="C18" s="29"/>
       <c r="D18" s="16">
         <v>1</v>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="41">
         <v>45964</v>
       </c>
-      <c r="F18" s="42">
+      <c r="F18" s="41">
         <v>45967</v>
       </c>
-      <c r="G18" s="50"/>
+      <c r="G18" s="49"/>
       <c r="H18" s="12"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20"/>
-      <c r="T18" s="20"/>
-      <c r="U18" s="20"/>
-      <c r="V18" s="20"/>
-      <c r="W18" s="20"/>
-      <c r="X18" s="20"/>
-      <c r="Y18" s="20"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="20"/>
-      <c r="AB18" s="20"/>
-      <c r="AC18" s="20"/>
-      <c r="AD18" s="20"/>
-      <c r="AE18" s="20"/>
-      <c r="AF18" s="20"/>
-      <c r="AG18" s="20"/>
-      <c r="AH18" s="20"/>
-      <c r="AI18" s="20"/>
-      <c r="AJ18" s="20"/>
-      <c r="AK18" s="80"/>
-      <c r="AL18" s="80"/>
-      <c r="AM18" s="20"/>
-      <c r="AN18" s="20"/>
-      <c r="AO18" s="20"/>
-      <c r="AP18" s="20"/>
-      <c r="AQ18" s="20"/>
-      <c r="AR18" s="20"/>
-      <c r="AS18" s="20"/>
-      <c r="AT18" s="20"/>
-      <c r="AU18" s="20"/>
-      <c r="AV18" s="20"/>
-      <c r="AW18" s="20"/>
-      <c r="AX18" s="20"/>
-      <c r="AY18" s="20"/>
-      <c r="AZ18" s="20"/>
-      <c r="BA18" s="20"/>
-      <c r="BB18" s="20"/>
-      <c r="BC18" s="20"/>
-      <c r="BD18" s="20"/>
-      <c r="BE18" s="20"/>
-      <c r="BF18" s="20"/>
-      <c r="BG18" s="20"/>
-      <c r="BH18" s="43"/>
-      <c r="BI18" s="20"/>
-      <c r="BJ18" s="20"/>
-      <c r="BK18" s="20"/>
-      <c r="BL18" s="20"/>
-      <c r="BM18" s="20"/>
-      <c r="BN18" s="20"/>
-      <c r="BO18" s="20"/>
-      <c r="BP18" s="80"/>
-      <c r="BQ18" s="43"/>
-      <c r="BR18" s="43"/>
-      <c r="BS18" s="43"/>
-      <c r="BT18" s="43"/>
-      <c r="BU18" s="43"/>
-      <c r="BV18" s="43"/>
-      <c r="BW18" s="20"/>
-      <c r="BX18" s="20"/>
-      <c r="BY18" s="20"/>
-      <c r="BZ18" s="43"/>
-      <c r="CA18" s="43"/>
-      <c r="CB18" s="43"/>
-      <c r="CC18" s="43"/>
-      <c r="CD18" s="43"/>
-      <c r="CE18" s="43"/>
-      <c r="CF18" s="43"/>
-      <c r="CG18" s="76"/>
-      <c r="CH18" s="20"/>
-      <c r="CI18" s="20"/>
-      <c r="CJ18" s="20"/>
-      <c r="CK18" s="20"/>
-      <c r="CL18" s="20"/>
-      <c r="CM18" s="20"/>
-      <c r="CN18" s="20"/>
-      <c r="CO18" s="73"/>
-      <c r="CP18" s="86"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19"/>
+      <c r="X18" s="19"/>
+      <c r="Y18" s="19"/>
+      <c r="Z18" s="19"/>
+      <c r="AA18" s="19"/>
+      <c r="AB18" s="19"/>
+      <c r="AC18" s="19"/>
+      <c r="AD18" s="19"/>
+      <c r="AE18" s="19"/>
+      <c r="AF18" s="19"/>
+      <c r="AG18" s="19"/>
+      <c r="AH18" s="19"/>
+      <c r="AI18" s="19"/>
+      <c r="AJ18" s="19"/>
+      <c r="AK18" s="78"/>
+      <c r="AL18" s="78"/>
+      <c r="AM18" s="19"/>
+      <c r="AN18" s="19"/>
+      <c r="AO18" s="19"/>
+      <c r="AP18" s="19"/>
+      <c r="AQ18" s="19"/>
+      <c r="AR18" s="19"/>
+      <c r="AS18" s="19"/>
+      <c r="AT18" s="19"/>
+      <c r="AU18" s="19"/>
+      <c r="AV18" s="19"/>
+      <c r="AW18" s="19"/>
+      <c r="AX18" s="19"/>
+      <c r="AY18" s="19"/>
+      <c r="AZ18" s="19"/>
+      <c r="BA18" s="19"/>
+      <c r="BB18" s="19"/>
+      <c r="BC18" s="19"/>
+      <c r="BD18" s="19"/>
+      <c r="BE18" s="19"/>
+      <c r="BF18" s="19"/>
+      <c r="BG18" s="19"/>
+      <c r="BH18" s="42"/>
+      <c r="BI18" s="19"/>
+      <c r="BJ18" s="19"/>
+      <c r="BK18" s="19"/>
+      <c r="BL18" s="19"/>
+      <c r="BM18" s="19"/>
+      <c r="BN18" s="19"/>
+      <c r="BO18" s="19"/>
+      <c r="BP18" s="78"/>
+      <c r="BQ18" s="42"/>
+      <c r="BR18" s="42"/>
+      <c r="BS18" s="42"/>
+      <c r="BT18" s="42"/>
+      <c r="BU18" s="42"/>
+      <c r="BV18" s="42"/>
+      <c r="BW18" s="19"/>
+      <c r="BX18" s="19"/>
+      <c r="BY18" s="19"/>
+      <c r="BZ18" s="42"/>
+      <c r="CA18" s="42"/>
+      <c r="CB18" s="42"/>
+      <c r="CC18" s="42"/>
+      <c r="CD18" s="42"/>
+      <c r="CE18" s="42"/>
+      <c r="CF18" s="42"/>
+      <c r="CG18" s="74"/>
+      <c r="CH18" s="19"/>
+      <c r="CI18" s="19"/>
+      <c r="CJ18" s="19"/>
+      <c r="CK18" s="19"/>
+      <c r="CL18" s="19"/>
+      <c r="CM18" s="19"/>
+      <c r="CN18" s="19"/>
+      <c r="CO18" s="71"/>
+      <c r="CP18" s="84"/>
       <c r="CQ18"/>
       <c r="CR18"/>
       <c r="CS18"/>
@@ -4594,108 +4588,108 @@
       <c r="DQ18"/>
     </row>
     <row r="19" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24"/>
-      <c r="B19" s="33" t="s">
+      <c r="A19" s="23"/>
+      <c r="B19" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="30"/>
+      <c r="C19" s="29"/>
       <c r="D19" s="16">
-        <v>0</v>
-      </c>
-      <c r="E19" s="42">
+        <v>1</v>
+      </c>
+      <c r="E19" s="41">
         <v>45968</v>
       </c>
-      <c r="F19" s="42">
+      <c r="F19" s="41">
         <v>45972</v>
       </c>
-      <c r="G19" s="50"/>
+      <c r="G19" s="49"/>
       <c r="H19" s="12"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="20"/>
-      <c r="T19" s="20"/>
-      <c r="U19" s="20"/>
-      <c r="V19" s="20"/>
-      <c r="W19" s="20"/>
-      <c r="X19" s="20"/>
-      <c r="Y19" s="20"/>
-      <c r="Z19" s="20"/>
-      <c r="AA19" s="20"/>
-      <c r="AB19" s="20"/>
-      <c r="AC19" s="20"/>
-      <c r="AD19" s="20"/>
-      <c r="AE19" s="20"/>
-      <c r="AF19" s="20"/>
-      <c r="AG19" s="20"/>
-      <c r="AH19" s="20"/>
-      <c r="AI19" s="20"/>
-      <c r="AJ19" s="20"/>
-      <c r="AK19" s="80"/>
-      <c r="AL19" s="80"/>
-      <c r="AM19" s="20"/>
-      <c r="AN19" s="20"/>
-      <c r="AO19" s="20"/>
-      <c r="AP19" s="20"/>
-      <c r="AQ19" s="20"/>
-      <c r="AR19" s="20"/>
-      <c r="AS19" s="20"/>
-      <c r="AT19" s="20"/>
-      <c r="AU19" s="20"/>
-      <c r="AV19" s="20"/>
-      <c r="AW19" s="20"/>
-      <c r="AX19" s="20"/>
-      <c r="AY19" s="20"/>
-      <c r="AZ19" s="20"/>
-      <c r="BA19" s="20"/>
-      <c r="BB19" s="20"/>
-      <c r="BC19" s="20"/>
-      <c r="BD19" s="20"/>
-      <c r="BE19" s="20"/>
-      <c r="BF19" s="20"/>
-      <c r="BG19" s="20"/>
-      <c r="BH19" s="43"/>
-      <c r="BI19" s="20"/>
-      <c r="BJ19" s="20"/>
-      <c r="BK19" s="20"/>
-      <c r="BL19" s="20"/>
-      <c r="BM19" s="20"/>
-      <c r="BN19" s="20"/>
-      <c r="BO19" s="20"/>
-      <c r="BP19" s="80"/>
-      <c r="BQ19" s="43"/>
-      <c r="BR19" s="20"/>
-      <c r="BS19" s="43"/>
-      <c r="BT19" s="43"/>
-      <c r="BU19" s="20"/>
-      <c r="BV19" s="20"/>
-      <c r="BW19" s="20"/>
-      <c r="BX19" s="20"/>
-      <c r="BY19" s="20"/>
-      <c r="BZ19" s="43"/>
-      <c r="CA19" s="20"/>
-      <c r="CB19" s="43"/>
-      <c r="CC19" s="43"/>
-      <c r="CD19" s="43"/>
-      <c r="CE19" s="43"/>
-      <c r="CF19" s="43"/>
-      <c r="CG19" s="76"/>
-      <c r="CH19" s="20"/>
-      <c r="CI19" s="20"/>
-      <c r="CJ19" s="20"/>
-      <c r="CK19" s="20"/>
-      <c r="CL19" s="20"/>
-      <c r="CM19" s="20"/>
-      <c r="CN19" s="20"/>
-      <c r="CO19" s="73"/>
-      <c r="CP19" s="86"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="19"/>
+      <c r="Y19" s="19"/>
+      <c r="Z19" s="19"/>
+      <c r="AA19" s="19"/>
+      <c r="AB19" s="19"/>
+      <c r="AC19" s="19"/>
+      <c r="AD19" s="19"/>
+      <c r="AE19" s="19"/>
+      <c r="AF19" s="19"/>
+      <c r="AG19" s="19"/>
+      <c r="AH19" s="19"/>
+      <c r="AI19" s="19"/>
+      <c r="AJ19" s="19"/>
+      <c r="AK19" s="78"/>
+      <c r="AL19" s="78"/>
+      <c r="AM19" s="19"/>
+      <c r="AN19" s="19"/>
+      <c r="AO19" s="19"/>
+      <c r="AP19" s="19"/>
+      <c r="AQ19" s="19"/>
+      <c r="AR19" s="19"/>
+      <c r="AS19" s="19"/>
+      <c r="AT19" s="19"/>
+      <c r="AU19" s="19"/>
+      <c r="AV19" s="19"/>
+      <c r="AW19" s="19"/>
+      <c r="AX19" s="19"/>
+      <c r="AY19" s="19"/>
+      <c r="AZ19" s="19"/>
+      <c r="BA19" s="19"/>
+      <c r="BB19" s="19"/>
+      <c r="BC19" s="19"/>
+      <c r="BD19" s="19"/>
+      <c r="BE19" s="19"/>
+      <c r="BF19" s="19"/>
+      <c r="BG19" s="19"/>
+      <c r="BH19" s="42"/>
+      <c r="BI19" s="19"/>
+      <c r="BJ19" s="19"/>
+      <c r="BK19" s="19"/>
+      <c r="BL19" s="19"/>
+      <c r="BM19" s="19"/>
+      <c r="BN19" s="19"/>
+      <c r="BO19" s="19"/>
+      <c r="BP19" s="78"/>
+      <c r="BQ19" s="42"/>
+      <c r="BR19" s="19"/>
+      <c r="BS19" s="42"/>
+      <c r="BT19" s="42"/>
+      <c r="BU19" s="19"/>
+      <c r="BV19" s="19"/>
+      <c r="BW19" s="19"/>
+      <c r="BX19" s="19"/>
+      <c r="BY19" s="19"/>
+      <c r="BZ19" s="42"/>
+      <c r="CA19" s="19"/>
+      <c r="CB19" s="42"/>
+      <c r="CC19" s="42"/>
+      <c r="CD19" s="42"/>
+      <c r="CE19" s="42"/>
+      <c r="CF19" s="42"/>
+      <c r="CG19" s="74"/>
+      <c r="CH19" s="19"/>
+      <c r="CI19" s="19"/>
+      <c r="CJ19" s="19"/>
+      <c r="CK19" s="19"/>
+      <c r="CL19" s="19"/>
+      <c r="CM19" s="19"/>
+      <c r="CN19" s="19"/>
+      <c r="CO19" s="71"/>
+      <c r="CP19" s="84"/>
       <c r="CQ19"/>
       <c r="CR19"/>
       <c r="CS19"/>
@@ -4725,108 +4719,108 @@
       <c r="DQ19"/>
     </row>
     <row r="20" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="24"/>
-      <c r="B20" s="33" t="s">
+      <c r="A20" s="23"/>
+      <c r="B20" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="30"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="16">
-        <v>0</v>
-      </c>
-      <c r="E20" s="42">
+        <v>1</v>
+      </c>
+      <c r="E20" s="41">
         <v>45972</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="41">
         <v>45974</v>
       </c>
-      <c r="G20" s="50"/>
+      <c r="G20" s="49"/>
       <c r="H20" s="12"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
-      <c r="T20" s="20"/>
-      <c r="U20" s="20"/>
-      <c r="V20" s="20"/>
-      <c r="W20" s="20"/>
-      <c r="X20" s="20"/>
-      <c r="Y20" s="20"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="20"/>
-      <c r="AB20" s="20"/>
-      <c r="AC20" s="20"/>
-      <c r="AD20" s="20"/>
-      <c r="AE20" s="20"/>
-      <c r="AF20" s="20"/>
-      <c r="AG20" s="20"/>
-      <c r="AH20" s="20"/>
-      <c r="AI20" s="20"/>
-      <c r="AJ20" s="20"/>
-      <c r="AK20" s="80"/>
-      <c r="AL20" s="80"/>
-      <c r="AM20" s="20"/>
-      <c r="AN20" s="20"/>
-      <c r="AO20" s="20"/>
-      <c r="AP20" s="20"/>
-      <c r="AQ20" s="20"/>
-      <c r="AR20" s="20"/>
-      <c r="AS20" s="20"/>
-      <c r="AT20" s="20"/>
-      <c r="AU20" s="20"/>
-      <c r="AV20" s="20"/>
-      <c r="AW20" s="20"/>
-      <c r="AX20" s="20"/>
-      <c r="AY20" s="20"/>
-      <c r="AZ20" s="20"/>
-      <c r="BA20" s="20"/>
-      <c r="BB20" s="20"/>
-      <c r="BC20" s="20"/>
-      <c r="BD20" s="20"/>
-      <c r="BE20" s="20"/>
-      <c r="BF20" s="20"/>
-      <c r="BG20" s="20"/>
-      <c r="BH20" s="43"/>
-      <c r="BI20" s="20"/>
-      <c r="BJ20" s="20"/>
-      <c r="BK20" s="20"/>
-      <c r="BL20" s="20"/>
-      <c r="BM20" s="20"/>
-      <c r="BN20" s="20"/>
-      <c r="BO20" s="20"/>
-      <c r="BP20" s="80"/>
-      <c r="BQ20" s="43"/>
-      <c r="BR20" s="43"/>
-      <c r="BS20" s="43"/>
-      <c r="BT20" s="43"/>
-      <c r="BU20" s="43"/>
-      <c r="BV20" s="43"/>
-      <c r="BW20" s="43"/>
-      <c r="BX20" s="43"/>
-      <c r="BY20" s="43"/>
-      <c r="BZ20" s="43"/>
-      <c r="CA20" s="43"/>
-      <c r="CB20" s="43"/>
-      <c r="CC20" s="43"/>
-      <c r="CD20" s="43"/>
-      <c r="CE20" s="43"/>
-      <c r="CF20" s="43"/>
-      <c r="CG20" s="76"/>
-      <c r="CH20" s="20"/>
-      <c r="CI20" s="20"/>
-      <c r="CJ20" s="20"/>
-      <c r="CK20" s="20"/>
-      <c r="CL20" s="20"/>
-      <c r="CM20" s="20"/>
-      <c r="CN20" s="20"/>
-      <c r="CO20" s="73"/>
-      <c r="CP20" s="86"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="19"/>
+      <c r="U20" s="19"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="19"/>
+      <c r="X20" s="19"/>
+      <c r="Y20" s="19"/>
+      <c r="Z20" s="19"/>
+      <c r="AA20" s="19"/>
+      <c r="AB20" s="19"/>
+      <c r="AC20" s="19"/>
+      <c r="AD20" s="19"/>
+      <c r="AE20" s="19"/>
+      <c r="AF20" s="19"/>
+      <c r="AG20" s="19"/>
+      <c r="AH20" s="19"/>
+      <c r="AI20" s="19"/>
+      <c r="AJ20" s="19"/>
+      <c r="AK20" s="78"/>
+      <c r="AL20" s="78"/>
+      <c r="AM20" s="19"/>
+      <c r="AN20" s="19"/>
+      <c r="AO20" s="19"/>
+      <c r="AP20" s="19"/>
+      <c r="AQ20" s="19"/>
+      <c r="AR20" s="19"/>
+      <c r="AS20" s="19"/>
+      <c r="AT20" s="19"/>
+      <c r="AU20" s="19"/>
+      <c r="AV20" s="19"/>
+      <c r="AW20" s="19"/>
+      <c r="AX20" s="19"/>
+      <c r="AY20" s="19"/>
+      <c r="AZ20" s="19"/>
+      <c r="BA20" s="19"/>
+      <c r="BB20" s="19"/>
+      <c r="BC20" s="19"/>
+      <c r="BD20" s="19"/>
+      <c r="BE20" s="19"/>
+      <c r="BF20" s="19"/>
+      <c r="BG20" s="19"/>
+      <c r="BH20" s="42"/>
+      <c r="BI20" s="19"/>
+      <c r="BJ20" s="19"/>
+      <c r="BK20" s="19"/>
+      <c r="BL20" s="19"/>
+      <c r="BM20" s="19"/>
+      <c r="BN20" s="19"/>
+      <c r="BO20" s="19"/>
+      <c r="BP20" s="78"/>
+      <c r="BQ20" s="42"/>
+      <c r="BR20" s="42"/>
+      <c r="BS20" s="42"/>
+      <c r="BT20" s="42"/>
+      <c r="BU20" s="42"/>
+      <c r="BV20" s="42"/>
+      <c r="BW20" s="42"/>
+      <c r="BX20" s="42"/>
+      <c r="BY20" s="42"/>
+      <c r="BZ20" s="42"/>
+      <c r="CA20" s="42"/>
+      <c r="CB20" s="42"/>
+      <c r="CC20" s="42"/>
+      <c r="CD20" s="42"/>
+      <c r="CE20" s="42"/>
+      <c r="CF20" s="42"/>
+      <c r="CG20" s="74"/>
+      <c r="CH20" s="19"/>
+      <c r="CI20" s="19"/>
+      <c r="CJ20" s="19"/>
+      <c r="CK20" s="19"/>
+      <c r="CL20" s="19"/>
+      <c r="CM20" s="19"/>
+      <c r="CN20" s="19"/>
+      <c r="CO20" s="71"/>
+      <c r="CP20" s="84"/>
       <c r="CQ20"/>
       <c r="CR20"/>
       <c r="CS20"/>
@@ -4856,108 +4850,108 @@
       <c r="DQ20"/>
     </row>
     <row r="21" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
-      <c r="B21" s="33" t="s">
+      <c r="A21" s="23"/>
+      <c r="B21" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="30"/>
+      <c r="C21" s="29"/>
       <c r="D21" s="16">
-        <v>0</v>
-      </c>
-      <c r="E21" s="42">
+        <v>1</v>
+      </c>
+      <c r="E21" s="41">
         <v>45975</v>
       </c>
-      <c r="F21" s="42">
+      <c r="F21" s="41">
         <v>45979</v>
       </c>
-      <c r="G21" s="50"/>
+      <c r="G21" s="49"/>
       <c r="H21" s="12"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
-      <c r="U21" s="20"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="20"/>
-      <c r="X21" s="20"/>
-      <c r="Y21" s="20"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="20"/>
-      <c r="AD21" s="20"/>
-      <c r="AE21" s="20"/>
-      <c r="AF21" s="20"/>
-      <c r="AG21" s="20"/>
-      <c r="AH21" s="20"/>
-      <c r="AI21" s="20"/>
-      <c r="AJ21" s="20"/>
-      <c r="AK21" s="80"/>
-      <c r="AL21" s="80"/>
-      <c r="AM21" s="20"/>
-      <c r="AN21" s="20"/>
-      <c r="AO21" s="20"/>
-      <c r="AP21" s="20"/>
-      <c r="AQ21" s="20"/>
-      <c r="AR21" s="20"/>
-      <c r="AS21" s="20"/>
-      <c r="AT21" s="20"/>
-      <c r="AU21" s="20"/>
-      <c r="AV21" s="20"/>
-      <c r="AW21" s="20"/>
-      <c r="AX21" s="20"/>
-      <c r="AY21" s="20"/>
-      <c r="AZ21" s="20"/>
-      <c r="BA21" s="20"/>
-      <c r="BB21" s="20"/>
-      <c r="BC21" s="20"/>
-      <c r="BD21" s="20"/>
-      <c r="BE21" s="20"/>
-      <c r="BF21" s="20"/>
-      <c r="BG21" s="20"/>
-      <c r="BH21" s="20"/>
-      <c r="BI21" s="20"/>
-      <c r="BJ21" s="20"/>
-      <c r="BK21" s="20"/>
-      <c r="BL21" s="20"/>
-      <c r="BM21" s="20"/>
-      <c r="BN21" s="20"/>
-      <c r="BO21" s="20"/>
-      <c r="BP21" s="80"/>
-      <c r="BQ21" s="43"/>
-      <c r="BR21" s="43"/>
-      <c r="BS21" s="43"/>
-      <c r="BT21" s="43"/>
-      <c r="BU21" s="43"/>
-      <c r="BV21" s="43"/>
-      <c r="BW21" s="43"/>
-      <c r="BX21" s="43"/>
-      <c r="BY21" s="43"/>
-      <c r="BZ21" s="43"/>
-      <c r="CA21" s="43"/>
-      <c r="CB21" s="43"/>
-      <c r="CC21" s="43"/>
-      <c r="CD21" s="43"/>
-      <c r="CE21" s="43"/>
-      <c r="CF21" s="43"/>
-      <c r="CG21" s="76"/>
-      <c r="CH21" s="20"/>
-      <c r="CI21" s="20"/>
-      <c r="CJ21" s="20"/>
-      <c r="CK21" s="20"/>
-      <c r="CL21" s="20"/>
-      <c r="CM21" s="20"/>
-      <c r="CN21" s="20"/>
-      <c r="CO21" s="73"/>
-      <c r="CP21" s="86"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="19"/>
+      <c r="U21" s="19"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="19"/>
+      <c r="X21" s="19"/>
+      <c r="Y21" s="19"/>
+      <c r="Z21" s="19"/>
+      <c r="AA21" s="19"/>
+      <c r="AB21" s="19"/>
+      <c r="AC21" s="19"/>
+      <c r="AD21" s="19"/>
+      <c r="AE21" s="19"/>
+      <c r="AF21" s="19"/>
+      <c r="AG21" s="19"/>
+      <c r="AH21" s="19"/>
+      <c r="AI21" s="19"/>
+      <c r="AJ21" s="19"/>
+      <c r="AK21" s="78"/>
+      <c r="AL21" s="78"/>
+      <c r="AM21" s="19"/>
+      <c r="AN21" s="19"/>
+      <c r="AO21" s="19"/>
+      <c r="AP21" s="19"/>
+      <c r="AQ21" s="19"/>
+      <c r="AR21" s="19"/>
+      <c r="AS21" s="19"/>
+      <c r="AT21" s="19"/>
+      <c r="AU21" s="19"/>
+      <c r="AV21" s="19"/>
+      <c r="AW21" s="19"/>
+      <c r="AX21" s="19"/>
+      <c r="AY21" s="19"/>
+      <c r="AZ21" s="19"/>
+      <c r="BA21" s="19"/>
+      <c r="BB21" s="19"/>
+      <c r="BC21" s="19"/>
+      <c r="BD21" s="19"/>
+      <c r="BE21" s="19"/>
+      <c r="BF21" s="19"/>
+      <c r="BG21" s="19"/>
+      <c r="BH21" s="19"/>
+      <c r="BI21" s="19"/>
+      <c r="BJ21" s="19"/>
+      <c r="BK21" s="19"/>
+      <c r="BL21" s="19"/>
+      <c r="BM21" s="19"/>
+      <c r="BN21" s="19"/>
+      <c r="BO21" s="19"/>
+      <c r="BP21" s="78"/>
+      <c r="BQ21" s="42"/>
+      <c r="BR21" s="42"/>
+      <c r="BS21" s="42"/>
+      <c r="BT21" s="42"/>
+      <c r="BU21" s="42"/>
+      <c r="BV21" s="42"/>
+      <c r="BW21" s="42"/>
+      <c r="BX21" s="42"/>
+      <c r="BY21" s="42"/>
+      <c r="BZ21" s="42"/>
+      <c r="CA21" s="42"/>
+      <c r="CB21" s="42"/>
+      <c r="CC21" s="42"/>
+      <c r="CD21" s="42"/>
+      <c r="CE21" s="42"/>
+      <c r="CF21" s="42"/>
+      <c r="CG21" s="74"/>
+      <c r="CH21" s="19"/>
+      <c r="CI21" s="19"/>
+      <c r="CJ21" s="19"/>
+      <c r="CK21" s="19"/>
+      <c r="CL21" s="19"/>
+      <c r="CM21" s="19"/>
+      <c r="CN21" s="19"/>
+      <c r="CO21" s="71"/>
+      <c r="CP21" s="84"/>
       <c r="CQ21"/>
       <c r="CR21"/>
       <c r="CS21"/>
@@ -4987,107 +4981,107 @@
       <c r="DQ21"/>
     </row>
     <row r="22" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="31"/>
+      <c r="C22" s="30"/>
       <c r="D22" s="18"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="51"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="50"/>
       <c r="H22" s="12" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="89"/>
-      <c r="L22" s="89"/>
-      <c r="M22" s="89"/>
-      <c r="N22" s="89"/>
-      <c r="O22" s="89"/>
-      <c r="P22" s="89"/>
-      <c r="Q22" s="89"/>
-      <c r="R22" s="89"/>
-      <c r="S22" s="89"/>
-      <c r="T22" s="89"/>
-      <c r="U22" s="89"/>
-      <c r="V22" s="89"/>
-      <c r="W22" s="89"/>
-      <c r="X22" s="89"/>
-      <c r="Y22" s="89"/>
-      <c r="Z22" s="89"/>
-      <c r="AA22" s="89"/>
-      <c r="AB22" s="89"/>
-      <c r="AC22" s="89"/>
-      <c r="AD22" s="89"/>
-      <c r="AE22" s="89"/>
-      <c r="AF22" s="89"/>
-      <c r="AG22" s="89"/>
-      <c r="AH22" s="89"/>
-      <c r="AI22" s="89"/>
-      <c r="AJ22" s="89"/>
-      <c r="AK22" s="89"/>
-      <c r="AL22" s="89"/>
-      <c r="AM22" s="89"/>
-      <c r="AN22" s="89"/>
-      <c r="AO22" s="89"/>
-      <c r="AP22" s="89"/>
-      <c r="AQ22" s="89"/>
-      <c r="AR22" s="89"/>
-      <c r="AS22" s="89"/>
-      <c r="AT22" s="89"/>
-      <c r="AU22" s="89"/>
-      <c r="AV22" s="89"/>
-      <c r="AW22" s="89"/>
-      <c r="AX22" s="89"/>
-      <c r="AY22" s="89"/>
-      <c r="AZ22" s="89"/>
-      <c r="BA22" s="89"/>
-      <c r="BB22" s="89"/>
-      <c r="BC22" s="89"/>
-      <c r="BD22" s="89"/>
-      <c r="BE22" s="89"/>
-      <c r="BF22" s="89"/>
-      <c r="BG22" s="89"/>
-      <c r="BH22" s="89"/>
-      <c r="BI22" s="89"/>
-      <c r="BJ22" s="89"/>
-      <c r="BK22" s="89"/>
-      <c r="BL22" s="89"/>
-      <c r="BM22" s="89"/>
-      <c r="BN22" s="89"/>
-      <c r="BO22" s="89"/>
-      <c r="BP22" s="89"/>
-      <c r="BQ22" s="89"/>
-      <c r="BR22" s="89"/>
-      <c r="BS22" s="89"/>
-      <c r="BT22" s="89"/>
-      <c r="BU22" s="89"/>
-      <c r="BV22" s="89"/>
-      <c r="BW22" s="89"/>
-      <c r="BX22" s="89"/>
-      <c r="BY22" s="89"/>
-      <c r="BZ22" s="89"/>
-      <c r="CA22" s="89"/>
-      <c r="CB22" s="89"/>
-      <c r="CC22" s="89"/>
-      <c r="CD22" s="89"/>
-      <c r="CE22" s="89"/>
-      <c r="CF22" s="89"/>
-      <c r="CG22" s="89"/>
-      <c r="CH22" s="89"/>
-      <c r="CI22" s="89"/>
-      <c r="CJ22" s="89"/>
-      <c r="CK22" s="89"/>
-      <c r="CL22" s="89"/>
-      <c r="CM22" s="89"/>
-      <c r="CN22" s="89"/>
-      <c r="CO22" s="89"/>
-      <c r="CP22" s="86"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="91"/>
+      <c r="K22" s="91"/>
+      <c r="L22" s="91"/>
+      <c r="M22" s="91"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="91"/>
+      <c r="P22" s="91"/>
+      <c r="Q22" s="91"/>
+      <c r="R22" s="91"/>
+      <c r="S22" s="91"/>
+      <c r="T22" s="91"/>
+      <c r="U22" s="91"/>
+      <c r="V22" s="91"/>
+      <c r="W22" s="91"/>
+      <c r="X22" s="91"/>
+      <c r="Y22" s="91"/>
+      <c r="Z22" s="91"/>
+      <c r="AA22" s="91"/>
+      <c r="AB22" s="91"/>
+      <c r="AC22" s="91"/>
+      <c r="AD22" s="91"/>
+      <c r="AE22" s="91"/>
+      <c r="AF22" s="91"/>
+      <c r="AG22" s="91"/>
+      <c r="AH22" s="91"/>
+      <c r="AI22" s="91"/>
+      <c r="AJ22" s="91"/>
+      <c r="AK22" s="91"/>
+      <c r="AL22" s="91"/>
+      <c r="AM22" s="91"/>
+      <c r="AN22" s="91"/>
+      <c r="AO22" s="91"/>
+      <c r="AP22" s="91"/>
+      <c r="AQ22" s="91"/>
+      <c r="AR22" s="91"/>
+      <c r="AS22" s="91"/>
+      <c r="AT22" s="91"/>
+      <c r="AU22" s="91"/>
+      <c r="AV22" s="91"/>
+      <c r="AW22" s="91"/>
+      <c r="AX22" s="91"/>
+      <c r="AY22" s="91"/>
+      <c r="AZ22" s="91"/>
+      <c r="BA22" s="91"/>
+      <c r="BB22" s="91"/>
+      <c r="BC22" s="91"/>
+      <c r="BD22" s="91"/>
+      <c r="BE22" s="91"/>
+      <c r="BF22" s="91"/>
+      <c r="BG22" s="91"/>
+      <c r="BH22" s="91"/>
+      <c r="BI22" s="91"/>
+      <c r="BJ22" s="91"/>
+      <c r="BK22" s="91"/>
+      <c r="BL22" s="91"/>
+      <c r="BM22" s="91"/>
+      <c r="BN22" s="91"/>
+      <c r="BO22" s="91"/>
+      <c r="BP22" s="91"/>
+      <c r="BQ22" s="91"/>
+      <c r="BR22" s="91"/>
+      <c r="BS22" s="91"/>
+      <c r="BT22" s="91"/>
+      <c r="BU22" s="91"/>
+      <c r="BV22" s="91"/>
+      <c r="BW22" s="91"/>
+      <c r="BX22" s="91"/>
+      <c r="BY22" s="91"/>
+      <c r="BZ22" s="91"/>
+      <c r="CA22" s="91"/>
+      <c r="CB22" s="91"/>
+      <c r="CC22" s="91"/>
+      <c r="CD22" s="91"/>
+      <c r="CE22" s="91"/>
+      <c r="CF22" s="91"/>
+      <c r="CG22" s="91"/>
+      <c r="CH22" s="91"/>
+      <c r="CI22" s="91"/>
+      <c r="CJ22" s="91"/>
+      <c r="CK22" s="91"/>
+      <c r="CL22" s="91"/>
+      <c r="CM22" s="91"/>
+      <c r="CN22" s="91"/>
+      <c r="CO22" s="91"/>
+      <c r="CP22" s="84"/>
       <c r="CQ22"/>
       <c r="CR22"/>
       <c r="CS22"/>
@@ -5117,111 +5111,111 @@
       <c r="DQ22"/>
     </row>
     <row r="23" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="23"/>
-      <c r="B23" s="60" t="s">
+      <c r="A23" s="22"/>
+      <c r="B23" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="19">
-        <v>0</v>
-      </c>
-      <c r="E23" s="39">
+      <c r="C23" s="31"/>
+      <c r="D23" s="16">
+        <v>1</v>
+      </c>
+      <c r="E23" s="38">
         <v>45980</v>
       </c>
-      <c r="F23" s="39">
+      <c r="F23" s="38">
         <v>45981</v>
       </c>
-      <c r="G23" s="52"/>
+      <c r="G23" s="51"/>
       <c r="H23" s="12">
         <f t="shared" si="25"/>
         <v>2</v>
       </c>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
-      <c r="T23" s="20"/>
-      <c r="U23" s="20"/>
-      <c r="V23" s="20"/>
-      <c r="W23" s="20"/>
-      <c r="X23" s="20"/>
-      <c r="Y23" s="20"/>
-      <c r="Z23" s="20"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="20"/>
-      <c r="AC23" s="43"/>
-      <c r="AD23" s="43"/>
-      <c r="AE23" s="20"/>
-      <c r="AF23" s="20"/>
-      <c r="AG23" s="20"/>
-      <c r="AH23" s="20"/>
-      <c r="AI23" s="20"/>
-      <c r="AJ23" s="20"/>
-      <c r="AK23" s="80"/>
-      <c r="AL23" s="80"/>
-      <c r="AM23" s="20"/>
-      <c r="AN23" s="20"/>
-      <c r="AO23" s="20"/>
-      <c r="AP23" s="20"/>
-      <c r="AQ23" s="20"/>
-      <c r="AR23" s="20"/>
-      <c r="AS23" s="20"/>
-      <c r="AT23" s="20"/>
-      <c r="AU23" s="20"/>
-      <c r="AV23" s="20"/>
-      <c r="AW23" s="20"/>
-      <c r="AX23" s="20"/>
-      <c r="AY23" s="20"/>
-      <c r="AZ23" s="20"/>
-      <c r="BA23" s="20"/>
-      <c r="BB23" s="20"/>
-      <c r="BC23" s="20"/>
-      <c r="BD23" s="20"/>
-      <c r="BE23" s="20"/>
-      <c r="BF23" s="20"/>
-      <c r="BG23" s="20"/>
-      <c r="BH23" s="43"/>
-      <c r="BI23" s="20"/>
-      <c r="BJ23" s="20"/>
-      <c r="BK23" s="20"/>
-      <c r="BL23" s="20"/>
-      <c r="BM23" s="20"/>
-      <c r="BN23" s="20"/>
-      <c r="BO23" s="20"/>
-      <c r="BP23" s="80"/>
-      <c r="BQ23" s="43"/>
-      <c r="BR23" s="43"/>
-      <c r="BS23" s="43"/>
-      <c r="BT23" s="43"/>
-      <c r="BU23" s="43"/>
-      <c r="BV23" s="43"/>
-      <c r="BW23" s="43"/>
-      <c r="BX23" s="43"/>
-      <c r="BY23" s="43"/>
-      <c r="BZ23" s="43"/>
-      <c r="CA23" s="43"/>
-      <c r="CB23" s="43"/>
-      <c r="CC23" s="43"/>
-      <c r="CD23" s="43"/>
-      <c r="CE23" s="43"/>
-      <c r="CF23" s="43"/>
-      <c r="CG23" s="76"/>
-      <c r="CH23" s="20"/>
-      <c r="CI23" s="20"/>
-      <c r="CJ23" s="20"/>
-      <c r="CK23" s="20"/>
-      <c r="CL23" s="20"/>
-      <c r="CM23" s="20"/>
-      <c r="CN23" s="20"/>
-      <c r="CO23" s="73"/>
-      <c r="CP23" s="86"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="19"/>
+      <c r="U23" s="19"/>
+      <c r="V23" s="19"/>
+      <c r="W23" s="19"/>
+      <c r="X23" s="19"/>
+      <c r="Y23" s="19"/>
+      <c r="Z23" s="19"/>
+      <c r="AA23" s="19"/>
+      <c r="AB23" s="19"/>
+      <c r="AC23" s="42"/>
+      <c r="AD23" s="42"/>
+      <c r="AE23" s="19"/>
+      <c r="AF23" s="19"/>
+      <c r="AG23" s="19"/>
+      <c r="AH23" s="19"/>
+      <c r="AI23" s="19"/>
+      <c r="AJ23" s="19"/>
+      <c r="AK23" s="78"/>
+      <c r="AL23" s="78"/>
+      <c r="AM23" s="19"/>
+      <c r="AN23" s="19"/>
+      <c r="AO23" s="19"/>
+      <c r="AP23" s="19"/>
+      <c r="AQ23" s="19"/>
+      <c r="AR23" s="19"/>
+      <c r="AS23" s="19"/>
+      <c r="AT23" s="19"/>
+      <c r="AU23" s="19"/>
+      <c r="AV23" s="19"/>
+      <c r="AW23" s="19"/>
+      <c r="AX23" s="19"/>
+      <c r="AY23" s="19"/>
+      <c r="AZ23" s="19"/>
+      <c r="BA23" s="19"/>
+      <c r="BB23" s="19"/>
+      <c r="BC23" s="19"/>
+      <c r="BD23" s="19"/>
+      <c r="BE23" s="19"/>
+      <c r="BF23" s="19"/>
+      <c r="BG23" s="19"/>
+      <c r="BH23" s="42"/>
+      <c r="BI23" s="19"/>
+      <c r="BJ23" s="19"/>
+      <c r="BK23" s="19"/>
+      <c r="BL23" s="19"/>
+      <c r="BM23" s="19"/>
+      <c r="BN23" s="19"/>
+      <c r="BO23" s="19"/>
+      <c r="BP23" s="78"/>
+      <c r="BQ23" s="42"/>
+      <c r="BR23" s="42"/>
+      <c r="BS23" s="42"/>
+      <c r="BT23" s="42"/>
+      <c r="BU23" s="42"/>
+      <c r="BV23" s="42"/>
+      <c r="BW23" s="42"/>
+      <c r="BX23" s="42"/>
+      <c r="BY23" s="42"/>
+      <c r="BZ23" s="42"/>
+      <c r="CA23" s="42"/>
+      <c r="CB23" s="42"/>
+      <c r="CC23" s="42"/>
+      <c r="CD23" s="42"/>
+      <c r="CE23" s="42"/>
+      <c r="CF23" s="42"/>
+      <c r="CG23" s="74"/>
+      <c r="CH23" s="19"/>
+      <c r="CI23" s="19"/>
+      <c r="CJ23" s="19"/>
+      <c r="CK23" s="19"/>
+      <c r="CL23" s="19"/>
+      <c r="CM23" s="19"/>
+      <c r="CN23" s="19"/>
+      <c r="CO23" s="71"/>
+      <c r="CP23" s="84"/>
       <c r="CQ23"/>
       <c r="CR23"/>
       <c r="CS23"/>
@@ -5251,111 +5245,111 @@
       <c r="DQ23"/>
     </row>
     <row r="24" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="23"/>
-      <c r="B24" s="60" t="s">
+      <c r="A24" s="22"/>
+      <c r="B24" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="19">
-        <v>0</v>
-      </c>
-      <c r="E24" s="39">
+      <c r="C24" s="31"/>
+      <c r="D24" s="16">
+        <v>1</v>
+      </c>
+      <c r="E24" s="38">
         <v>45980</v>
       </c>
-      <c r="F24" s="39">
+      <c r="F24" s="38">
         <v>45982</v>
       </c>
-      <c r="G24" s="52"/>
+      <c r="G24" s="51"/>
       <c r="H24" s="12">
         <f t="shared" si="25"/>
         <v>3</v>
       </c>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="20"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20"/>
-      <c r="X24" s="20"/>
-      <c r="Y24" s="20"/>
-      <c r="Z24" s="20"/>
-      <c r="AA24" s="20"/>
-      <c r="AB24" s="20"/>
-      <c r="AC24" s="43"/>
-      <c r="AD24" s="43"/>
-      <c r="AE24" s="20"/>
-      <c r="AF24" s="20"/>
-      <c r="AG24" s="20"/>
-      <c r="AH24" s="20"/>
-      <c r="AI24" s="20"/>
-      <c r="AJ24" s="20"/>
-      <c r="AK24" s="80"/>
-      <c r="AL24" s="80"/>
-      <c r="AM24" s="20"/>
-      <c r="AN24" s="20"/>
-      <c r="AO24" s="20"/>
-      <c r="AP24" s="20"/>
-      <c r="AQ24" s="20"/>
-      <c r="AR24" s="20"/>
-      <c r="AS24" s="20"/>
-      <c r="AT24" s="20"/>
-      <c r="AU24" s="20"/>
-      <c r="AV24" s="20"/>
-      <c r="AW24" s="20"/>
-      <c r="AX24" s="20"/>
-      <c r="AY24" s="20"/>
-      <c r="AZ24" s="20"/>
-      <c r="BA24" s="20"/>
-      <c r="BB24" s="20"/>
-      <c r="BC24" s="20"/>
-      <c r="BD24" s="20"/>
-      <c r="BE24" s="20"/>
-      <c r="BF24" s="20"/>
-      <c r="BG24" s="20"/>
-      <c r="BH24" s="43"/>
-      <c r="BI24" s="20"/>
-      <c r="BJ24" s="20"/>
-      <c r="BK24" s="20"/>
-      <c r="BL24" s="20"/>
-      <c r="BM24" s="20"/>
-      <c r="BN24" s="20"/>
-      <c r="BO24" s="20"/>
-      <c r="BP24" s="80"/>
-      <c r="BQ24" s="43"/>
-      <c r="BR24" s="43"/>
-      <c r="BS24" s="43"/>
-      <c r="BT24" s="43"/>
-      <c r="BU24" s="43"/>
-      <c r="BV24" s="43"/>
-      <c r="BW24" s="43"/>
-      <c r="BX24" s="43"/>
-      <c r="BY24" s="43"/>
-      <c r="BZ24" s="43"/>
-      <c r="CA24" s="43"/>
-      <c r="CB24" s="43"/>
-      <c r="CC24" s="43"/>
-      <c r="CD24" s="43"/>
-      <c r="CE24" s="43"/>
-      <c r="CF24" s="43"/>
-      <c r="CG24" s="76"/>
-      <c r="CH24" s="20"/>
-      <c r="CI24" s="20"/>
-      <c r="CJ24" s="20"/>
-      <c r="CK24" s="20"/>
-      <c r="CL24" s="20"/>
-      <c r="CM24" s="20"/>
-      <c r="CN24" s="20"/>
-      <c r="CO24" s="73"/>
-      <c r="CP24" s="86"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="19"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="19"/>
+      <c r="X24" s="19"/>
+      <c r="Y24" s="19"/>
+      <c r="Z24" s="19"/>
+      <c r="AA24" s="19"/>
+      <c r="AB24" s="19"/>
+      <c r="AC24" s="42"/>
+      <c r="AD24" s="42"/>
+      <c r="AE24" s="19"/>
+      <c r="AF24" s="19"/>
+      <c r="AG24" s="19"/>
+      <c r="AH24" s="19"/>
+      <c r="AI24" s="19"/>
+      <c r="AJ24" s="19"/>
+      <c r="AK24" s="78"/>
+      <c r="AL24" s="78"/>
+      <c r="AM24" s="19"/>
+      <c r="AN24" s="19"/>
+      <c r="AO24" s="19"/>
+      <c r="AP24" s="19"/>
+      <c r="AQ24" s="19"/>
+      <c r="AR24" s="19"/>
+      <c r="AS24" s="19"/>
+      <c r="AT24" s="19"/>
+      <c r="AU24" s="19"/>
+      <c r="AV24" s="19"/>
+      <c r="AW24" s="19"/>
+      <c r="AX24" s="19"/>
+      <c r="AY24" s="19"/>
+      <c r="AZ24" s="19"/>
+      <c r="BA24" s="19"/>
+      <c r="BB24" s="19"/>
+      <c r="BC24" s="19"/>
+      <c r="BD24" s="19"/>
+      <c r="BE24" s="19"/>
+      <c r="BF24" s="19"/>
+      <c r="BG24" s="19"/>
+      <c r="BH24" s="42"/>
+      <c r="BI24" s="19"/>
+      <c r="BJ24" s="19"/>
+      <c r="BK24" s="19"/>
+      <c r="BL24" s="19"/>
+      <c r="BM24" s="19"/>
+      <c r="BN24" s="19"/>
+      <c r="BO24" s="19"/>
+      <c r="BP24" s="78"/>
+      <c r="BQ24" s="42"/>
+      <c r="BR24" s="42"/>
+      <c r="BS24" s="42"/>
+      <c r="BT24" s="42"/>
+      <c r="BU24" s="42"/>
+      <c r="BV24" s="42"/>
+      <c r="BW24" s="42"/>
+      <c r="BX24" s="42"/>
+      <c r="BY24" s="42"/>
+      <c r="BZ24" s="42"/>
+      <c r="CA24" s="42"/>
+      <c r="CB24" s="42"/>
+      <c r="CC24" s="42"/>
+      <c r="CD24" s="42"/>
+      <c r="CE24" s="42"/>
+      <c r="CF24" s="42"/>
+      <c r="CG24" s="74"/>
+      <c r="CH24" s="19"/>
+      <c r="CI24" s="19"/>
+      <c r="CJ24" s="19"/>
+      <c r="CK24" s="19"/>
+      <c r="CL24" s="19"/>
+      <c r="CM24" s="19"/>
+      <c r="CN24" s="19"/>
+      <c r="CO24" s="71"/>
+      <c r="CP24" s="84"/>
       <c r="CQ24"/>
       <c r="CR24"/>
       <c r="CS24"/>
@@ -5385,108 +5379,108 @@
       <c r="DQ24"/>
     </row>
     <row r="25" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="23"/>
-      <c r="B25" s="60" t="s">
+      <c r="A25" s="22"/>
+      <c r="B25" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="19">
-        <v>0</v>
-      </c>
-      <c r="E25" s="39">
+      <c r="C25" s="31"/>
+      <c r="D25" s="16">
+        <v>1</v>
+      </c>
+      <c r="E25" s="38">
         <v>45985</v>
       </c>
-      <c r="F25" s="39">
+      <c r="F25" s="38">
         <v>45986</v>
       </c>
-      <c r="G25" s="52"/>
+      <c r="G25" s="51"/>
       <c r="H25" s="12"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
-      <c r="U25" s="20"/>
-      <c r="V25" s="20"/>
-      <c r="W25" s="20"/>
-      <c r="X25" s="20"/>
-      <c r="Y25" s="20"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="20"/>
-      <c r="AB25" s="20"/>
-      <c r="AC25" s="43"/>
-      <c r="AD25" s="43"/>
-      <c r="AE25" s="20"/>
-      <c r="AF25" s="20"/>
-      <c r="AG25" s="20"/>
-      <c r="AH25" s="20"/>
-      <c r="AI25" s="20"/>
-      <c r="AJ25" s="20"/>
-      <c r="AK25" s="80"/>
-      <c r="AL25" s="80"/>
-      <c r="AM25" s="20"/>
-      <c r="AN25" s="20"/>
-      <c r="AO25" s="20"/>
-      <c r="AP25" s="20"/>
-      <c r="AQ25" s="20"/>
-      <c r="AR25" s="20"/>
-      <c r="AS25" s="20"/>
-      <c r="AT25" s="20"/>
-      <c r="AU25" s="20"/>
-      <c r="AV25" s="20"/>
-      <c r="AW25" s="20"/>
-      <c r="AX25" s="20"/>
-      <c r="AY25" s="20"/>
-      <c r="AZ25" s="20"/>
-      <c r="BA25" s="20"/>
-      <c r="BB25" s="20"/>
-      <c r="BC25" s="20"/>
-      <c r="BD25" s="20"/>
-      <c r="BE25" s="20"/>
-      <c r="BF25" s="20"/>
-      <c r="BG25" s="20"/>
-      <c r="BH25" s="43"/>
-      <c r="BI25" s="20"/>
-      <c r="BJ25" s="20"/>
-      <c r="BK25" s="20"/>
-      <c r="BL25" s="20"/>
-      <c r="BM25" s="20"/>
-      <c r="BN25" s="20"/>
-      <c r="BO25" s="20"/>
-      <c r="BP25" s="80"/>
-      <c r="BQ25" s="43"/>
-      <c r="BR25" s="43"/>
-      <c r="BS25" s="43"/>
-      <c r="BT25" s="43"/>
-      <c r="BU25" s="43"/>
-      <c r="BV25" s="43"/>
-      <c r="BW25" s="43"/>
-      <c r="BX25" s="43"/>
-      <c r="BY25" s="43"/>
-      <c r="BZ25" s="43"/>
-      <c r="CA25" s="43"/>
-      <c r="CB25" s="43"/>
-      <c r="CC25" s="43"/>
-      <c r="CD25" s="43"/>
-      <c r="CE25" s="43"/>
-      <c r="CF25" s="43"/>
-      <c r="CG25" s="76"/>
-      <c r="CH25" s="20"/>
-      <c r="CI25" s="20"/>
-      <c r="CJ25" s="20"/>
-      <c r="CK25" s="20"/>
-      <c r="CL25" s="20"/>
-      <c r="CM25" s="20"/>
-      <c r="CN25" s="20"/>
-      <c r="CO25" s="73"/>
-      <c r="CP25" s="86"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="19"/>
+      <c r="Y25" s="19"/>
+      <c r="Z25" s="19"/>
+      <c r="AA25" s="19"/>
+      <c r="AB25" s="19"/>
+      <c r="AC25" s="42"/>
+      <c r="AD25" s="42"/>
+      <c r="AE25" s="19"/>
+      <c r="AF25" s="19"/>
+      <c r="AG25" s="19"/>
+      <c r="AH25" s="19"/>
+      <c r="AI25" s="19"/>
+      <c r="AJ25" s="19"/>
+      <c r="AK25" s="78"/>
+      <c r="AL25" s="78"/>
+      <c r="AM25" s="19"/>
+      <c r="AN25" s="19"/>
+      <c r="AO25" s="19"/>
+      <c r="AP25" s="19"/>
+      <c r="AQ25" s="19"/>
+      <c r="AR25" s="19"/>
+      <c r="AS25" s="19"/>
+      <c r="AT25" s="19"/>
+      <c r="AU25" s="19"/>
+      <c r="AV25" s="19"/>
+      <c r="AW25" s="19"/>
+      <c r="AX25" s="19"/>
+      <c r="AY25" s="19"/>
+      <c r="AZ25" s="19"/>
+      <c r="BA25" s="19"/>
+      <c r="BB25" s="19"/>
+      <c r="BC25" s="19"/>
+      <c r="BD25" s="19"/>
+      <c r="BE25" s="19"/>
+      <c r="BF25" s="19"/>
+      <c r="BG25" s="19"/>
+      <c r="BH25" s="42"/>
+      <c r="BI25" s="19"/>
+      <c r="BJ25" s="19"/>
+      <c r="BK25" s="19"/>
+      <c r="BL25" s="19"/>
+      <c r="BM25" s="19"/>
+      <c r="BN25" s="19"/>
+      <c r="BO25" s="19"/>
+      <c r="BP25" s="78"/>
+      <c r="BQ25" s="42"/>
+      <c r="BR25" s="42"/>
+      <c r="BS25" s="42"/>
+      <c r="BT25" s="42"/>
+      <c r="BU25" s="42"/>
+      <c r="BV25" s="42"/>
+      <c r="BW25" s="42"/>
+      <c r="BX25" s="42"/>
+      <c r="BY25" s="42"/>
+      <c r="BZ25" s="42"/>
+      <c r="CA25" s="42"/>
+      <c r="CB25" s="42"/>
+      <c r="CC25" s="42"/>
+      <c r="CD25" s="42"/>
+      <c r="CE25" s="42"/>
+      <c r="CF25" s="42"/>
+      <c r="CG25" s="74"/>
+      <c r="CH25" s="19"/>
+      <c r="CI25" s="19"/>
+      <c r="CJ25" s="19"/>
+      <c r="CK25" s="19"/>
+      <c r="CL25" s="19"/>
+      <c r="CM25" s="19"/>
+      <c r="CN25" s="19"/>
+      <c r="CO25" s="71"/>
+      <c r="CP25" s="84"/>
       <c r="CQ25"/>
       <c r="CR25"/>
       <c r="CS25"/>
@@ -5516,111 +5510,111 @@
       <c r="DQ25"/>
     </row>
     <row r="26" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="23"/>
-      <c r="B26" s="60" t="s">
+      <c r="A26" s="22"/>
+      <c r="B26" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="19">
-        <v>0</v>
-      </c>
-      <c r="E26" s="39">
+      <c r="C26" s="31"/>
+      <c r="D26" s="16">
+        <v>1</v>
+      </c>
+      <c r="E26" s="38">
         <v>45987</v>
       </c>
-      <c r="F26" s="39">
+      <c r="F26" s="38">
         <v>45988</v>
       </c>
-      <c r="G26" s="52"/>
+      <c r="G26" s="51"/>
       <c r="H26" s="12">
         <f t="shared" si="25"/>
         <v>2</v>
       </c>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
-      <c r="U26" s="20"/>
-      <c r="V26" s="20"/>
-      <c r="W26" s="20"/>
-      <c r="X26" s="20"/>
-      <c r="Y26" s="20"/>
-      <c r="Z26" s="20"/>
-      <c r="AA26" s="20"/>
-      <c r="AB26" s="20"/>
-      <c r="AC26" s="43"/>
-      <c r="AD26" s="43"/>
-      <c r="AE26" s="20"/>
-      <c r="AF26" s="20"/>
-      <c r="AG26" s="20"/>
-      <c r="AH26" s="20"/>
-      <c r="AI26" s="20"/>
-      <c r="AJ26" s="20"/>
-      <c r="AK26" s="80"/>
-      <c r="AL26" s="80"/>
-      <c r="AM26" s="20"/>
-      <c r="AN26" s="20"/>
-      <c r="AO26" s="20"/>
-      <c r="AP26" s="20"/>
-      <c r="AQ26" s="20"/>
-      <c r="AR26" s="20"/>
-      <c r="AS26" s="20"/>
-      <c r="AT26" s="20"/>
-      <c r="AU26" s="20"/>
-      <c r="AV26" s="20"/>
-      <c r="AW26" s="20"/>
-      <c r="AX26" s="20"/>
-      <c r="AY26" s="20"/>
-      <c r="AZ26" s="20"/>
-      <c r="BA26" s="20"/>
-      <c r="BB26" s="20"/>
-      <c r="BC26" s="20"/>
-      <c r="BD26" s="20"/>
-      <c r="BE26" s="20"/>
-      <c r="BF26" s="20"/>
-      <c r="BG26" s="20"/>
-      <c r="BH26" s="43"/>
-      <c r="BI26" s="20"/>
-      <c r="BJ26" s="20"/>
-      <c r="BK26" s="20"/>
-      <c r="BL26" s="20"/>
-      <c r="BM26" s="20"/>
-      <c r="BN26" s="20"/>
-      <c r="BO26" s="20"/>
-      <c r="BP26" s="80"/>
-      <c r="BQ26" s="43"/>
-      <c r="BR26" s="43"/>
-      <c r="BS26" s="43"/>
-      <c r="BT26" s="43"/>
-      <c r="BU26" s="43"/>
-      <c r="BV26" s="43"/>
-      <c r="BW26" s="43"/>
-      <c r="BX26" s="43"/>
-      <c r="BY26" s="43"/>
-      <c r="BZ26" s="43"/>
-      <c r="CA26" s="43"/>
-      <c r="CB26" s="43"/>
-      <c r="CC26" s="43"/>
-      <c r="CD26" s="43"/>
-      <c r="CE26" s="43"/>
-      <c r="CF26" s="43"/>
-      <c r="CG26" s="76"/>
-      <c r="CH26" s="20"/>
-      <c r="CI26" s="20"/>
-      <c r="CJ26" s="20"/>
-      <c r="CK26" s="20"/>
-      <c r="CL26" s="20"/>
-      <c r="CM26" s="20"/>
-      <c r="CN26" s="20"/>
-      <c r="CO26" s="73"/>
-      <c r="CP26" s="86"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="19"/>
+      <c r="Y26" s="19"/>
+      <c r="Z26" s="19"/>
+      <c r="AA26" s="19"/>
+      <c r="AB26" s="19"/>
+      <c r="AC26" s="42"/>
+      <c r="AD26" s="42"/>
+      <c r="AE26" s="19"/>
+      <c r="AF26" s="19"/>
+      <c r="AG26" s="19"/>
+      <c r="AH26" s="19"/>
+      <c r="AI26" s="19"/>
+      <c r="AJ26" s="19"/>
+      <c r="AK26" s="78"/>
+      <c r="AL26" s="78"/>
+      <c r="AM26" s="19"/>
+      <c r="AN26" s="19"/>
+      <c r="AO26" s="19"/>
+      <c r="AP26" s="19"/>
+      <c r="AQ26" s="19"/>
+      <c r="AR26" s="19"/>
+      <c r="AS26" s="19"/>
+      <c r="AT26" s="19"/>
+      <c r="AU26" s="19"/>
+      <c r="AV26" s="19"/>
+      <c r="AW26" s="19"/>
+      <c r="AX26" s="19"/>
+      <c r="AY26" s="19"/>
+      <c r="AZ26" s="19"/>
+      <c r="BA26" s="19"/>
+      <c r="BB26" s="19"/>
+      <c r="BC26" s="19"/>
+      <c r="BD26" s="19"/>
+      <c r="BE26" s="19"/>
+      <c r="BF26" s="19"/>
+      <c r="BG26" s="19"/>
+      <c r="BH26" s="42"/>
+      <c r="BI26" s="19"/>
+      <c r="BJ26" s="19"/>
+      <c r="BK26" s="19"/>
+      <c r="BL26" s="19"/>
+      <c r="BM26" s="19"/>
+      <c r="BN26" s="19"/>
+      <c r="BO26" s="19"/>
+      <c r="BP26" s="78"/>
+      <c r="BQ26" s="42"/>
+      <c r="BR26" s="42"/>
+      <c r="BS26" s="42"/>
+      <c r="BT26" s="42"/>
+      <c r="BU26" s="42"/>
+      <c r="BV26" s="42"/>
+      <c r="BW26" s="42"/>
+      <c r="BX26" s="42"/>
+      <c r="BY26" s="42"/>
+      <c r="BZ26" s="42"/>
+      <c r="CA26" s="42"/>
+      <c r="CB26" s="42"/>
+      <c r="CC26" s="42"/>
+      <c r="CD26" s="42"/>
+      <c r="CE26" s="42"/>
+      <c r="CF26" s="42"/>
+      <c r="CG26" s="74"/>
+      <c r="CH26" s="19"/>
+      <c r="CI26" s="19"/>
+      <c r="CJ26" s="19"/>
+      <c r="CK26" s="19"/>
+      <c r="CL26" s="19"/>
+      <c r="CM26" s="19"/>
+      <c r="CN26" s="19"/>
+      <c r="CO26" s="71"/>
+      <c r="CP26" s="84"/>
       <c r="CQ26"/>
       <c r="CR26"/>
       <c r="CS26"/>
@@ -5650,111 +5644,111 @@
       <c r="DQ26"/>
     </row>
     <row r="27" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23"/>
-      <c r="B27" s="60" t="s">
+      <c r="A27" s="22"/>
+      <c r="B27" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="32"/>
-      <c r="D27" s="19">
-        <v>0</v>
-      </c>
-      <c r="E27" s="39">
+      <c r="C27" s="31"/>
+      <c r="D27" s="16">
+        <v>1</v>
+      </c>
+      <c r="E27" s="38">
         <v>45988</v>
       </c>
-      <c r="F27" s="39">
+      <c r="F27" s="38">
         <v>45988</v>
       </c>
-      <c r="G27" s="52"/>
+      <c r="G27" s="51"/>
       <c r="H27" s="12">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="20"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="43"/>
-      <c r="AD27" s="43"/>
-      <c r="AE27" s="20"/>
-      <c r="AF27" s="20"/>
-      <c r="AG27" s="20"/>
-      <c r="AH27" s="20"/>
-      <c r="AI27" s="20"/>
-      <c r="AJ27" s="20"/>
-      <c r="AK27" s="80"/>
-      <c r="AL27" s="80"/>
-      <c r="AM27" s="20"/>
-      <c r="AN27" s="20"/>
-      <c r="AO27" s="20"/>
-      <c r="AP27" s="20"/>
-      <c r="AQ27" s="20"/>
-      <c r="AR27" s="20"/>
-      <c r="AS27" s="20"/>
-      <c r="AT27" s="20"/>
-      <c r="AU27" s="20"/>
-      <c r="AV27" s="20"/>
-      <c r="AW27" s="20"/>
-      <c r="AX27" s="20"/>
-      <c r="AY27" s="20"/>
-      <c r="AZ27" s="20"/>
-      <c r="BA27" s="20"/>
-      <c r="BB27" s="20"/>
-      <c r="BC27" s="20"/>
-      <c r="BD27" s="20"/>
-      <c r="BE27" s="20"/>
-      <c r="BF27" s="20"/>
-      <c r="BG27" s="20"/>
-      <c r="BH27" s="43"/>
-      <c r="BI27" s="20"/>
-      <c r="BJ27" s="20"/>
-      <c r="BK27" s="20"/>
-      <c r="BL27" s="20"/>
-      <c r="BM27" s="20"/>
-      <c r="BN27" s="20"/>
-      <c r="BO27" s="20"/>
-      <c r="BP27" s="80"/>
-      <c r="BQ27" s="43"/>
-      <c r="BR27" s="43"/>
-      <c r="BS27" s="43"/>
-      <c r="BT27" s="43"/>
-      <c r="BU27" s="43"/>
-      <c r="BV27" s="43"/>
-      <c r="BW27" s="43"/>
-      <c r="BX27" s="43"/>
-      <c r="BY27" s="43"/>
-      <c r="BZ27" s="43"/>
-      <c r="CA27" s="43"/>
-      <c r="CB27" s="43"/>
-      <c r="CC27" s="43"/>
-      <c r="CD27" s="43"/>
-      <c r="CE27" s="43"/>
-      <c r="CF27" s="43"/>
-      <c r="CG27" s="76"/>
-      <c r="CH27" s="20"/>
-      <c r="CI27" s="20"/>
-      <c r="CJ27" s="20"/>
-      <c r="CK27" s="20"/>
-      <c r="CL27" s="20"/>
-      <c r="CM27" s="20"/>
-      <c r="CN27" s="20"/>
-      <c r="CO27" s="73"/>
-      <c r="CP27" s="86"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="19"/>
+      <c r="Y27" s="19"/>
+      <c r="Z27" s="19"/>
+      <c r="AA27" s="19"/>
+      <c r="AB27" s="19"/>
+      <c r="AC27" s="42"/>
+      <c r="AD27" s="42"/>
+      <c r="AE27" s="19"/>
+      <c r="AF27" s="19"/>
+      <c r="AG27" s="19"/>
+      <c r="AH27" s="19"/>
+      <c r="AI27" s="19"/>
+      <c r="AJ27" s="19"/>
+      <c r="AK27" s="78"/>
+      <c r="AL27" s="78"/>
+      <c r="AM27" s="19"/>
+      <c r="AN27" s="19"/>
+      <c r="AO27" s="19"/>
+      <c r="AP27" s="19"/>
+      <c r="AQ27" s="19"/>
+      <c r="AR27" s="19"/>
+      <c r="AS27" s="19"/>
+      <c r="AT27" s="19"/>
+      <c r="AU27" s="19"/>
+      <c r="AV27" s="19"/>
+      <c r="AW27" s="19"/>
+      <c r="AX27" s="19"/>
+      <c r="AY27" s="19"/>
+      <c r="AZ27" s="19"/>
+      <c r="BA27" s="19"/>
+      <c r="BB27" s="19"/>
+      <c r="BC27" s="19"/>
+      <c r="BD27" s="19"/>
+      <c r="BE27" s="19"/>
+      <c r="BF27" s="19"/>
+      <c r="BG27" s="19"/>
+      <c r="BH27" s="42"/>
+      <c r="BI27" s="19"/>
+      <c r="BJ27" s="19"/>
+      <c r="BK27" s="19"/>
+      <c r="BL27" s="19"/>
+      <c r="BM27" s="19"/>
+      <c r="BN27" s="19"/>
+      <c r="BO27" s="19"/>
+      <c r="BP27" s="78"/>
+      <c r="BQ27" s="42"/>
+      <c r="BR27" s="42"/>
+      <c r="BS27" s="42"/>
+      <c r="BT27" s="42"/>
+      <c r="BU27" s="42"/>
+      <c r="BV27" s="42"/>
+      <c r="BW27" s="42"/>
+      <c r="BX27" s="42"/>
+      <c r="BY27" s="42"/>
+      <c r="BZ27" s="42"/>
+      <c r="CA27" s="42"/>
+      <c r="CB27" s="42"/>
+      <c r="CC27" s="42"/>
+      <c r="CD27" s="42"/>
+      <c r="CE27" s="42"/>
+      <c r="CF27" s="42"/>
+      <c r="CG27" s="74"/>
+      <c r="CH27" s="19"/>
+      <c r="CI27" s="19"/>
+      <c r="CJ27" s="19"/>
+      <c r="CK27" s="19"/>
+      <c r="CL27" s="19"/>
+      <c r="CM27" s="19"/>
+      <c r="CN27" s="19"/>
+      <c r="CO27" s="71"/>
+      <c r="CP27" s="84"/>
       <c r="CQ27"/>
       <c r="CR27"/>
       <c r="CS27"/>
@@ -5783,112 +5777,112 @@
       <c r="DP27"/>
       <c r="DQ27"/>
     </row>
-    <row r="28" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="23"/>
-      <c r="B28" s="63" t="s">
+    <row r="28" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="22"/>
+      <c r="B28" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="64"/>
-      <c r="D28" s="65">
-        <v>0</v>
-      </c>
-      <c r="E28" s="66">
+      <c r="C28" s="63"/>
+      <c r="D28" s="16">
+        <v>1</v>
+      </c>
+      <c r="E28" s="64">
         <v>45988</v>
       </c>
-      <c r="F28" s="66">
+      <c r="F28" s="64">
         <v>45989</v>
       </c>
-      <c r="G28" s="67"/>
-      <c r="H28" s="68">
+      <c r="G28" s="65"/>
+      <c r="H28" s="66">
         <f t="shared" si="25"/>
         <v>2</v>
       </c>
-      <c r="I28" s="69"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="69"/>
-      <c r="L28" s="69"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="69"/>
-      <c r="O28" s="69"/>
-      <c r="P28" s="69"/>
-      <c r="Q28" s="69"/>
-      <c r="R28" s="69"/>
-      <c r="S28" s="69"/>
-      <c r="T28" s="69"/>
-      <c r="U28" s="69"/>
-      <c r="V28" s="69"/>
-      <c r="W28" s="69"/>
-      <c r="X28" s="69"/>
-      <c r="Y28" s="69"/>
-      <c r="Z28" s="69"/>
-      <c r="AA28" s="69"/>
-      <c r="AB28" s="69"/>
-      <c r="AC28" s="70"/>
-      <c r="AD28" s="70"/>
-      <c r="AE28" s="69"/>
-      <c r="AF28" s="69"/>
-      <c r="AG28" s="69"/>
-      <c r="AH28" s="69"/>
-      <c r="AI28" s="69"/>
-      <c r="AJ28" s="69"/>
-      <c r="AK28" s="81"/>
-      <c r="AL28" s="81"/>
-      <c r="AM28" s="69"/>
-      <c r="AN28" s="69"/>
-      <c r="AO28" s="69"/>
-      <c r="AP28" s="69"/>
-      <c r="AQ28" s="69"/>
-      <c r="AR28" s="69"/>
-      <c r="AS28" s="69"/>
-      <c r="AT28" s="69"/>
-      <c r="AU28" s="69"/>
-      <c r="AV28" s="69"/>
-      <c r="AW28" s="69"/>
-      <c r="AX28" s="69"/>
-      <c r="AY28" s="69"/>
-      <c r="AZ28" s="69"/>
-      <c r="BA28" s="69"/>
-      <c r="BB28" s="69"/>
-      <c r="BC28" s="69"/>
-      <c r="BD28" s="69"/>
-      <c r="BE28" s="69"/>
-      <c r="BF28" s="69"/>
-      <c r="BG28" s="69"/>
-      <c r="BH28" s="70"/>
-      <c r="BI28" s="69"/>
-      <c r="BJ28" s="69"/>
-      <c r="BK28" s="69"/>
-      <c r="BL28" s="69"/>
-      <c r="BM28" s="69"/>
-      <c r="BN28" s="69"/>
-      <c r="BO28" s="69"/>
-      <c r="BP28" s="81"/>
-      <c r="BQ28" s="70"/>
-      <c r="BR28" s="70"/>
-      <c r="BS28" s="70"/>
-      <c r="BT28" s="70"/>
-      <c r="BU28" s="70"/>
-      <c r="BV28" s="70"/>
-      <c r="BW28" s="70"/>
-      <c r="BX28" s="70"/>
-      <c r="BY28" s="70"/>
-      <c r="BZ28" s="70"/>
-      <c r="CA28" s="70"/>
-      <c r="CB28" s="70"/>
-      <c r="CC28" s="70"/>
-      <c r="CD28" s="70"/>
-      <c r="CE28" s="70"/>
-      <c r="CF28" s="70"/>
-      <c r="CG28" s="77"/>
-      <c r="CH28" s="69"/>
-      <c r="CI28" s="69"/>
-      <c r="CJ28" s="69"/>
-      <c r="CK28" s="69"/>
-      <c r="CL28" s="69"/>
-      <c r="CM28" s="69"/>
-      <c r="CN28" s="69"/>
-      <c r="CO28" s="83"/>
-      <c r="CP28" s="86"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="67"/>
+      <c r="M28" s="67"/>
+      <c r="N28" s="67"/>
+      <c r="O28" s="67"/>
+      <c r="P28" s="67"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="67"/>
+      <c r="T28" s="67"/>
+      <c r="U28" s="67"/>
+      <c r="V28" s="67"/>
+      <c r="W28" s="67"/>
+      <c r="X28" s="67"/>
+      <c r="Y28" s="67"/>
+      <c r="Z28" s="67"/>
+      <c r="AA28" s="67"/>
+      <c r="AB28" s="67"/>
+      <c r="AC28" s="68"/>
+      <c r="AD28" s="68"/>
+      <c r="AE28" s="67"/>
+      <c r="AF28" s="67"/>
+      <c r="AG28" s="67"/>
+      <c r="AH28" s="67"/>
+      <c r="AI28" s="67"/>
+      <c r="AJ28" s="67"/>
+      <c r="AK28" s="79"/>
+      <c r="AL28" s="79"/>
+      <c r="AM28" s="67"/>
+      <c r="AN28" s="67"/>
+      <c r="AO28" s="67"/>
+      <c r="AP28" s="67"/>
+      <c r="AQ28" s="67"/>
+      <c r="AR28" s="67"/>
+      <c r="AS28" s="67"/>
+      <c r="AT28" s="67"/>
+      <c r="AU28" s="67"/>
+      <c r="AV28" s="67"/>
+      <c r="AW28" s="67"/>
+      <c r="AX28" s="67"/>
+      <c r="AY28" s="67"/>
+      <c r="AZ28" s="67"/>
+      <c r="BA28" s="67"/>
+      <c r="BB28" s="67"/>
+      <c r="BC28" s="67"/>
+      <c r="BD28" s="67"/>
+      <c r="BE28" s="67"/>
+      <c r="BF28" s="67"/>
+      <c r="BG28" s="67"/>
+      <c r="BH28" s="68"/>
+      <c r="BI28" s="67"/>
+      <c r="BJ28" s="67"/>
+      <c r="BK28" s="67"/>
+      <c r="BL28" s="67"/>
+      <c r="BM28" s="67"/>
+      <c r="BN28" s="67"/>
+      <c r="BO28" s="67"/>
+      <c r="BP28" s="79"/>
+      <c r="BQ28" s="68"/>
+      <c r="BR28" s="68"/>
+      <c r="BS28" s="68"/>
+      <c r="BT28" s="68"/>
+      <c r="BU28" s="68"/>
+      <c r="BV28" s="68"/>
+      <c r="BW28" s="68"/>
+      <c r="BX28" s="68"/>
+      <c r="BY28" s="68"/>
+      <c r="BZ28" s="68"/>
+      <c r="CA28" s="68"/>
+      <c r="CB28" s="68"/>
+      <c r="CC28" s="68"/>
+      <c r="CD28" s="68"/>
+      <c r="CE28" s="68"/>
+      <c r="CF28" s="68"/>
+      <c r="CG28" s="75"/>
+      <c r="CH28" s="67"/>
+      <c r="CI28" s="67"/>
+      <c r="CJ28" s="67"/>
+      <c r="CK28" s="67"/>
+      <c r="CL28" s="67"/>
+      <c r="CM28" s="67"/>
+      <c r="CN28" s="67"/>
+      <c r="CO28" s="81"/>
+      <c r="CP28" s="84"/>
       <c r="CQ28"/>
       <c r="CR28"/>
       <c r="CS28"/>
@@ -5918,7 +5912,7 @@
       <c r="DQ28"/>
     </row>
     <row r="29" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="22" t="s">
         <v>8</v>
       </c>
       <c r="CH29"/>
@@ -5959,14 +5953,14 @@
       <c r="DQ29"/>
     </row>
     <row r="30" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23"/>
+      <c r="A30" s="22"/>
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30" s="5"/>
       <c r="F30"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="47"/>
+      <c r="H30" s="46"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -6077,14 +6071,14 @@
       <c r="DQ30"/>
     </row>
     <row r="31" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23"/>
+      <c r="A31" s="22"/>
       <c r="B31"/>
       <c r="C31" s="10"/>
       <c r="D31"/>
       <c r="E31" s="5"/>
-      <c r="F31" s="25"/>
+      <c r="F31" s="24"/>
       <c r="G31"/>
-      <c r="H31" s="47"/>
+      <c r="H31" s="46"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -6195,14 +6189,14 @@
       <c r="DQ31"/>
     </row>
     <row r="32" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="23"/>
+      <c r="A32" s="22"/>
       <c r="B32"/>
       <c r="C32" s="11"/>
       <c r="D32"/>
       <c r="E32" s="5"/>
       <c r="F32"/>
       <c r="G32"/>
-      <c r="H32" s="47"/>
+      <c r="H32" s="46"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -6313,14 +6307,14 @@
       <c r="DQ32"/>
     </row>
     <row r="33" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="23"/>
+      <c r="A33" s="22"/>
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33" s="5"/>
       <c r="F33"/>
       <c r="G33"/>
-      <c r="H33" s="47"/>
+      <c r="H33" s="46"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -6431,14 +6425,14 @@
       <c r="DQ33"/>
     </row>
     <row r="34" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23"/>
+      <c r="A34" s="22"/>
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34" s="5"/>
       <c r="F34"/>
       <c r="G34"/>
-      <c r="H34" s="47"/>
+      <c r="H34" s="46"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
@@ -6549,7 +6543,7 @@
       <c r="DQ34"/>
     </row>
     <row r="35" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="22" t="s">
         <v>9</v>
       </c>
       <c r="B35"/>
@@ -6558,7 +6552,7 @@
       <c r="E35" s="5"/>
       <c r="F35"/>
       <c r="G35"/>
-      <c r="H35" s="47"/>
+      <c r="H35" s="46"/>
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
@@ -6669,14 +6663,14 @@
       <c r="DQ35"/>
     </row>
     <row r="36" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
+      <c r="A36" s="23"/>
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
       <c r="E36" s="5"/>
       <c r="F36"/>
       <c r="G36"/>
-      <c r="H36" s="47"/>
+      <c r="H36" s="46"/>
       <c r="I36"/>
       <c r="J36"/>
       <c r="K36"/>
@@ -6788,19 +6782,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="CF3:CJ3"/>
-    <mergeCell ref="CK3:CO3"/>
-    <mergeCell ref="I7:CO7"/>
-    <mergeCell ref="BB3:BF3"/>
-    <mergeCell ref="BG3:BK3"/>
-    <mergeCell ref="BL3:BP3"/>
-    <mergeCell ref="BQ3:BU3"/>
-    <mergeCell ref="BV3:BZ3"/>
-    <mergeCell ref="AC3:AG3"/>
-    <mergeCell ref="AH3:AL3"/>
-    <mergeCell ref="AM3:AQ3"/>
-    <mergeCell ref="AR3:AV3"/>
-    <mergeCell ref="AW3:BA3"/>
     <mergeCell ref="I22:CO22"/>
     <mergeCell ref="I14:CO14"/>
     <mergeCell ref="C2:D2"/>
@@ -6817,6 +6798,19 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="CA3:CE3"/>
+    <mergeCell ref="CF3:CJ3"/>
+    <mergeCell ref="CK3:CO3"/>
+    <mergeCell ref="I7:CO7"/>
+    <mergeCell ref="BB3:BF3"/>
+    <mergeCell ref="BG3:BK3"/>
+    <mergeCell ref="BL3:BP3"/>
+    <mergeCell ref="BQ3:BU3"/>
+    <mergeCell ref="BV3:BZ3"/>
+    <mergeCell ref="AC3:AG3"/>
+    <mergeCell ref="AH3:AL3"/>
+    <mergeCell ref="AM3:AQ3"/>
+    <mergeCell ref="AR3:AV3"/>
+    <mergeCell ref="AW3:BA3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D35">
     <cfRule type="dataBar" priority="17">
@@ -7191,15 +7185,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -7217,6 +7202,15 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7241,14 +7235,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7258,4 +7244,12 @@
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>